--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_36.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2615428.909274106</v>
+        <v>2595173.102308509</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16862198.5188142</v>
+        <v>16862198.51881421</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16862198.5188142</v>
+        <v>16862198.51881421</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48339935.50256918</v>
+        <v>48339935.50256919</v>
       </c>
     </row>
   </sheetData>
@@ -666,13 +666,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
         <v>2.631744146312712</v>
       </c>
       <c r="H2" t="n">
-        <v>396.4818195075475</v>
+        <v>153.6092169231127</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>180.1708601348271</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>46.15445382677984</v>
+        <v>69.19791654604148</v>
       </c>
       <c r="T2" t="n">
         <v>181.7481445426342</v>
@@ -736,25 +736,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.137271724084</v>
       </c>
       <c r="H3" t="n">
-        <v>326.3514834128362</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>196.3905368347448</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>109.8805897452095</v>
+        <v>509.8805897452095</v>
       </c>
       <c r="S3" t="n">
-        <v>55.37720751178114</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>138.0537116604114</v>
+        <v>2.93021804770251</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1707371186773</v>
+        <v>0.170737118677323</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>386.7687045820108</v>
       </c>
     </row>
     <row r="4">
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.4202238360907208</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4202238360907208</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>2.631744146312693</v>
       </c>
       <c r="H5" t="n">
-        <v>396.4818195075475</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>106.6853807882123</v>
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>50.44201662735367</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>69.19791654604148</v>
+        <v>469.1979165460415</v>
       </c>
       <c r="T5" t="n">
         <v>181.7481445426342</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>239.2056695955684</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>292.5186253238753</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -982,16 +982,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.137271724084</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>326.3514834128362</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>196.3905368347448</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>96.20077452444184</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>109.8805897452095</v>
@@ -1030,7 +1030,7 @@
         <v>0.1707371186773138</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>160.7050042078905</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4202238360907208</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4202238360907208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>159.7591415618783</v>
+        <v>2.631744146312693</v>
       </c>
       <c r="H8" t="n">
-        <v>396.4818195075475</v>
+        <v>48.24126881770724</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>106.6853807882123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.00729272874059</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>204.7374779296249</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.137271724084</v>
+        <v>103.8877382511219</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>96.20077452444184</v>
       </c>
       <c r="R9" t="n">
         <v>109.8805897452095</v>
       </c>
       <c r="S9" t="n">
-        <v>55.37720751178112</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>402.9302180477025</v>
+        <v>2.930218047702496</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1707371186773138</v>
       </c>
       <c r="V9" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48.54914594591918</v>
+        <v>301.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>224.3632896068686</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>216.4818195075475</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>289.1979165460415</v>
       </c>
       <c r="T11" t="n">
-        <v>401.7481445426342</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>449.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>458.3734759809475</v>
+        <v>203.3955351056665</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>412.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>331.3174326828064</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>204.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>181.0999124455193</v>
@@ -1459,7 +1459,7 @@
         <v>159.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>145.137271724084</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.241439117118716e-11</v>
+        <v>1.665739546297118e-11</v>
       </c>
       <c r="R12" t="n">
-        <v>9.468497968737788</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>222.9302180477025</v>
+        <v>172.9794310941976</v>
       </c>
       <c r="U12" t="n">
         <v>220.1707371186773</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>44.28194577374975</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>130.1002335761559</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>85.81828780240619</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>222.9993129555745</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1614,13 +1614,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>145.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>142.0976344238159</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>137.4818195075475</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>210.1979165460415</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>322.7481445426342</v>
       </c>
       <c r="U14" t="n">
-        <v>390.1312462973544</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>370.8510241668239</v>
@@ -1668,10 +1668,10 @@
         <v>379.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>8.677408018336751</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>252.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1696,10 +1696,10 @@
         <v>80.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>66.13727172408394</v>
+        <v>66.13727172408397</v>
       </c>
       <c r="H15" t="n">
-        <v>67.35148341283623</v>
+        <v>67.35148341283622</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.141838871873915e-11</v>
+        <v>2.32005457751533</v>
       </c>
       <c r="R15" t="n">
         <v>250.8805897452095</v>
@@ -1738,7 +1738,7 @@
         <v>143.9302180477025</v>
       </c>
       <c r="U15" t="n">
-        <v>143.4907916961777</v>
+        <v>141.1707371186773</v>
       </c>
       <c r="V15" t="n">
         <v>155.5106671915202</v>
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>26.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>21.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>15.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1790,28 +1790,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>89.48008717417261</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>182.4834146812384</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>234.9188457634882</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>367.380356344671</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>317.2345658511597</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>57.25344253013652</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>28.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1842,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>91.15795048954818</v>
+        <v>190.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>73.31209808643958</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>210.1979165460415</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>322.7481445426342</v>
@@ -1899,13 +1899,13 @@
         <v>390.1312462973544</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>370.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>379.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>333.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>252.3174326828064</v>
@@ -1933,13 +1933,13 @@
         <v>80.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>66.13727172408397</v>
+        <v>66.13727172408394</v>
       </c>
       <c r="H18" t="n">
-        <v>67.35148341283622</v>
+        <v>67.35148341283623</v>
       </c>
       <c r="I18" t="n">
-        <v>2.320054577579715</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.32005457751533</v>
       </c>
       <c r="R18" t="n">
         <v>250.8805897452095</v>
@@ -2000,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>13.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>21.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>15.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>67.51638408549275</v>
+        <v>424.559266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>444.899177161479</v>
+        <v>260.0556557702327</v>
       </c>
       <c r="S19" t="n">
-        <v>94.57413544056038</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2085,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>36.93264684356029</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>145.8896287080119</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>182.8222755515719</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>322.7481445426342</v>
@@ -2164,13 +2164,13 @@
         <v>88.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>83.67209722191262</v>
+        <v>85.99215179941312</v>
       </c>
       <c r="F21" t="n">
         <v>80.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>68.45732630170329</v>
+        <v>66.13727172408397</v>
       </c>
       <c r="H21" t="n">
         <v>67.35148341283622</v>
@@ -2267,22 +2267,22 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>182.4834146812384</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>234.9188457634882</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>310.0776952265559</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>367.380356344671</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7.156870624603872</v>
       </c>
       <c r="R22" t="n">
-        <v>267.2126617511042</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>222.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>190.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>67.81530558833406</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>258.289883831328</v>
       </c>
       <c r="W23" t="n">
         <v>379.3734759809475</v>
@@ -2407,10 +2407,10 @@
         <v>80.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>66.13727172408394</v>
+        <v>66.13727172408397</v>
       </c>
       <c r="H24" t="n">
-        <v>67.35148341283623</v>
+        <v>67.35148341283622</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.32005457751713</v>
       </c>
       <c r="R24" t="n">
-        <v>253.20064432271</v>
+        <v>250.8805897452095</v>
       </c>
       <c r="S24" t="n">
         <v>196.3772075117811</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>310.0776952265559</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>239.7157450343518</v>
+        <v>374.5372269692749</v>
       </c>
       <c r="R25" t="n">
-        <v>444.8991771614789</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>177.000000000259</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,25 +2601,25 @@
         <v>9.17086013482708</v>
       </c>
       <c r="S26" t="n">
-        <v>177.0000000002651</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>177.0000000002648</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>146.730739864384</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>146.730739865173</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27">
@@ -2635,19 +2635,19 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>176.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>171.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>168.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>155.3514834128362</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>25.39053683474476</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>152.1595797519288</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>177.0000000002604</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>177.0000000002298</v>
+        <v>144.265036707763</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>113.5047230332333</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>109.9809048369565</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>50.19974879412526</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>36.86718945707739</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>28.17031021621619</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>55.37280983870968</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>156.7823999999155</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>178.0000000000281</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>156.7823999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>178.0000000000281</v>
+        <v>178</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>178.0000000000281</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2878,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>151.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.1372717240839</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>138.3514834128362</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>8.390536834744758</v>
+        <v>8.390536834744765</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,25 +2914,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>77.2668656904581</v>
+        <v>178</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>148.3918631652552</v>
       </c>
       <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
         <v>178</v>
       </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>99.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>38.23256606552745</v>
       </c>
       <c r="D31" t="n">
-        <v>97.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>36.28194577374977</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2999,22 +2999,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>19.86718945707739</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>11.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>38.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>33.58324591075995</v>
+        <v>99.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -3027,22 +3027,22 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>156.7823999999076</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>178.0000000000308</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>178.0000000000308</v>
+        <v>178</v>
       </c>
       <c r="F32" t="n">
-        <v>178.0000000000308</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>156.7823999999999</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>8.390536834744758</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3151,22 +3151,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>156.7823999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>148.3918631652552</v>
+        <v>178</v>
       </c>
       <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>178</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>178</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>178</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>131.1194639663154</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>32.00566362923675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3270,16 +3270,16 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>156.7823999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>178.0000000000571</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>178.0000000000571</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>178.0000000000571</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>156.7823999998287</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>178</v>
+        <v>55.8031955828157</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>173.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3355,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.1372717240839</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>138.3514834128362</v>
       </c>
       <c r="I36" t="n">
         <v>8.390536834744758</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>148.3918631652552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>89.26098524713959</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36.28194577374977</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>38.37280983870968</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>59.44364543010755</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>66.09928559078182</v>
       </c>
     </row>
     <row r="38">
@@ -3510,13 +3510,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>156.7824</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>156.782399999798</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>178.0000000000673</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>178.0000000000673</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>178.0000000000673</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39">
@@ -3583,7 +3583,7 @@
         <v>173.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>153.2919507197359</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3625,25 +3625,25 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>153.2919507197359</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
         <v>178</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3659,22 +3659,22 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>46.29459635955646</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>97.53621805555548</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>92.98090483695654</v>
       </c>
       <c r="F40" t="n">
-        <v>86.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2.878129279397696</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>36.28194577374975</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>41.85847871917585</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3710,16 +3710,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>19.86718945707739</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>11.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>38.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3735,13 +3735,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>61.92615907662549</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>146.0970192117877</v>
       </c>
       <c r="D41" t="n">
-        <v>178.0000000001117</v>
+        <v>178</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I41" t="n">
         <v>10.68538078821226</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>84.17086013482708</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>178.0000000001117</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>178.0000000001117</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3865,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>56.19108864081337</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="V42" t="n">
         <v>178</v>
@@ -3880,10 +3880,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>56.19108864081337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3911,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>39.57897354523934</v>
       </c>
       <c r="I43" t="n">
-        <v>39.57897354523934</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>50.09701921178772</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H44" t="n">
-        <v>178.0000000001582</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>106.6853807882123</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>178.0000000001582</v>
+        <v>178</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>50.09701921131326</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>178.0000000001582</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D45" t="n">
         <v>178</v>
@@ -4069,10 +4069,10 @@
         <v>60.58162547555811</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="I45" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4184,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.4202238360907173</v>
       </c>
       <c r="U46" t="n">
-        <v>0.4202238360907173</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>513.7093090420045</v>
+        <v>672.4238518860097</v>
       </c>
       <c r="C2" t="n">
-        <v>463.7349875844349</v>
+        <v>622.4495304284401</v>
       </c>
       <c r="D2" t="n">
-        <v>453.291395928021</v>
+        <v>612.0059387720262</v>
       </c>
       <c r="E2" t="n">
-        <v>448.8840326887597</v>
+        <v>607.5985755327649</v>
       </c>
       <c r="F2" t="n">
-        <v>443.945013791778</v>
+        <v>198.6191525953792</v>
       </c>
       <c r="G2" t="n">
-        <v>441.2866863712601</v>
+        <v>195.9608251748613</v>
       </c>
       <c r="H2" t="n">
         <v>40.8</v>
@@ -4324,49 +4324,49 @@
         <v>100.6883424103254</v>
       </c>
       <c r="K2" t="n">
-        <v>576.1661551929981</v>
+        <v>242.4406218073104</v>
       </c>
       <c r="L2" t="n">
-        <v>752.0223923789277</v>
+        <v>418.29685899324</v>
       </c>
       <c r="M2" t="n">
-        <v>1256.922392378928</v>
+        <v>752.0223923789275</v>
       </c>
       <c r="N2" t="n">
-        <v>1761.822392378928</v>
+        <v>1256.922392378927</v>
       </c>
       <c r="O2" t="n">
-        <v>1880.036123108616</v>
+        <v>1375.136123108616</v>
       </c>
       <c r="P2" t="n">
-        <v>2040</v>
+        <v>1535.1</v>
       </c>
       <c r="Q2" t="n">
         <v>2040</v>
       </c>
       <c r="R2" t="n">
-        <v>1858.009232187043</v>
+        <v>2040</v>
       </c>
       <c r="S2" t="n">
-        <v>1811.388571755953</v>
+        <v>1970.103114599958</v>
       </c>
       <c r="T2" t="n">
-        <v>1627.804587369453</v>
+        <v>1786.519130213459</v>
       </c>
       <c r="U2" t="n">
-        <v>1376.156863836772</v>
+        <v>1534.871406680778</v>
       </c>
       <c r="V2" t="n">
-        <v>1143.984112153112</v>
+        <v>1302.698654997117</v>
       </c>
       <c r="W2" t="n">
-        <v>903.2028232834678</v>
+        <v>1061.917366127473</v>
       </c>
       <c r="X2" t="n">
-        <v>708.9787490807731</v>
+        <v>867.6932919247784</v>
       </c>
       <c r="Y2" t="n">
-        <v>596.5368978860192</v>
+        <v>755.2514407300245</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1261.991115572913</v>
+        <v>1063.740607029963</v>
       </c>
       <c r="C3" t="n">
-        <v>897.2437292643081</v>
+        <v>1063.740607029963</v>
       </c>
       <c r="D3" t="n">
-        <v>897.2437292643081</v>
+        <v>712.2883980423848</v>
       </c>
       <c r="E3" t="n">
-        <v>897.2437292643081</v>
+        <v>712.2883980423848</v>
       </c>
       <c r="F3" t="n">
-        <v>897.2437292643081</v>
+        <v>369.2214865899838</v>
       </c>
       <c r="G3" t="n">
-        <v>568.8222426743242</v>
+        <v>40.8</v>
       </c>
       <c r="H3" t="n">
-        <v>239.1742796310553</v>
+        <v>40.8</v>
       </c>
       <c r="I3" t="n">
         <v>40.8</v>
@@ -4424,28 +4424,28 @@
         <v>2040</v>
       </c>
       <c r="R3" t="n">
-        <v>1929.009505307869</v>
+        <v>1524.969101267465</v>
       </c>
       <c r="S3" t="n">
-        <v>1873.072932063646</v>
+        <v>1524.969101267465</v>
       </c>
       <c r="T3" t="n">
-        <v>1733.624738467271</v>
+        <v>1522.009285057665</v>
       </c>
       <c r="U3" t="n">
-        <v>1329.411872690829</v>
+        <v>1521.836823321627</v>
       </c>
       <c r="V3" t="n">
-        <v>1314.754633103435</v>
+        <v>1507.179583734233</v>
       </c>
       <c r="W3" t="n">
-        <v>1282.054488750073</v>
+        <v>1474.479439380871</v>
       </c>
       <c r="X3" t="n">
-        <v>1261.991115572913</v>
+        <v>1454.416066203712</v>
       </c>
       <c r="Y3" t="n">
-        <v>1261.991115572913</v>
+        <v>1063.740607029963</v>
       </c>
     </row>
     <row r="4">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="C4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="D4" t="n">
         <v>40.8</v>
@@ -4509,22 +4509,22 @@
         <v>41.22446852130376</v>
       </c>
       <c r="T4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="U4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="V4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="W4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="X4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
       <c r="Y4" t="n">
-        <v>40.8</v>
+        <v>41.22446852130376</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>621.4723199391885</v>
+        <v>220.9856335679285</v>
       </c>
       <c r="C5" t="n">
-        <v>571.4979984816189</v>
+        <v>171.0113121103589</v>
       </c>
       <c r="D5" t="n">
-        <v>561.054406825205</v>
+        <v>160.5677204539449</v>
       </c>
       <c r="E5" t="n">
-        <v>556.6470435859437</v>
+        <v>156.1603572146837</v>
       </c>
       <c r="F5" t="n">
-        <v>551.708024688962</v>
+        <v>151.221338317702</v>
       </c>
       <c r="G5" t="n">
-        <v>549.0496972684442</v>
+        <v>148.5630108971841</v>
       </c>
       <c r="H5" t="n">
         <v>148.5630108971841</v>
@@ -4567,13 +4567,13 @@
         <v>844.2985482135351</v>
       </c>
       <c r="M5" t="n">
-        <v>844.2985482135352</v>
+        <v>1256.922392378927</v>
       </c>
       <c r="N5" t="n">
-        <v>911.9862692703111</v>
+        <v>1256.922392378927</v>
       </c>
       <c r="O5" t="n">
-        <v>1030.2</v>
+        <v>1375.136123108616</v>
       </c>
       <c r="P5" t="n">
         <v>1535.1</v>
@@ -4582,28 +4582,28 @@
         <v>2040</v>
       </c>
       <c r="R5" t="n">
-        <v>1989.048468053178</v>
+        <v>2040</v>
       </c>
       <c r="S5" t="n">
-        <v>1919.151582653136</v>
+        <v>1566.062710559554</v>
       </c>
       <c r="T5" t="n">
-        <v>1735.567598266637</v>
+        <v>1382.478726173055</v>
       </c>
       <c r="U5" t="n">
-        <v>1483.919874733956</v>
+        <v>1130.831002640374</v>
       </c>
       <c r="V5" t="n">
-        <v>1251.747123050296</v>
+        <v>898.6582509567132</v>
       </c>
       <c r="W5" t="n">
-        <v>1010.965834180652</v>
+        <v>657.8769620870692</v>
       </c>
       <c r="X5" t="n">
-        <v>816.741759977957</v>
+        <v>416.2550736066971</v>
       </c>
       <c r="Y5" t="n">
-        <v>704.2999087832031</v>
+        <v>303.8132224119431</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1705.347397480254</v>
+        <v>1266.407883199188</v>
       </c>
       <c r="C6" t="n">
-        <v>1409.874038567249</v>
+        <v>1266.407883199188</v>
       </c>
       <c r="D6" t="n">
-        <v>1058.42182957967</v>
+        <v>914.9556742116097</v>
       </c>
       <c r="E6" t="n">
-        <v>712.2883980423848</v>
+        <v>568.8222426743242</v>
       </c>
       <c r="F6" t="n">
-        <v>369.2214865899838</v>
+        <v>568.8222426743242</v>
       </c>
       <c r="G6" t="n">
-        <v>40.8</v>
+        <v>568.8222426743242</v>
       </c>
       <c r="H6" t="n">
-        <v>40.8</v>
+        <v>239.1742796310553</v>
       </c>
       <c r="I6" t="n">
         <v>40.8</v>
@@ -4640,10 +4640,10 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K6" t="n">
-        <v>506.3931913728449</v>
+        <v>506.5610117413805</v>
       </c>
       <c r="L6" t="n">
-        <v>907.2038982510639</v>
+        <v>907.3717186195995</v>
       </c>
       <c r="M6" t="n">
         <v>1144.358439993923</v>
@@ -4658,31 +4658,31 @@
         <v>2040</v>
       </c>
       <c r="Q6" t="n">
-        <v>1942.827500480362</v>
+        <v>2040</v>
       </c>
       <c r="R6" t="n">
-        <v>1831.837005788231</v>
+        <v>1929.009505307869</v>
       </c>
       <c r="S6" t="n">
-        <v>1775.900432544008</v>
+        <v>1873.072932063646</v>
       </c>
       <c r="T6" t="n">
-        <v>1772.940616334207</v>
+        <v>1870.113115853845</v>
       </c>
       <c r="U6" t="n">
-        <v>1772.768154598169</v>
+        <v>1869.940654117808</v>
       </c>
       <c r="V6" t="n">
-        <v>1758.110915010775</v>
+        <v>1707.61236703913</v>
       </c>
       <c r="W6" t="n">
-        <v>1725.410770657413</v>
+        <v>1674.912222685768</v>
       </c>
       <c r="X6" t="n">
-        <v>1705.347397480254</v>
+        <v>1654.848849508609</v>
       </c>
       <c r="Y6" t="n">
-        <v>1705.347397480254</v>
+        <v>1654.848849508609</v>
       </c>
     </row>
     <row r="7">
@@ -4749,16 +4749,16 @@
         <v>41.22446852130376</v>
       </c>
       <c r="U7" t="n">
-        <v>41.22446852130376</v>
+        <v>40.8</v>
       </c>
       <c r="V7" t="n">
-        <v>41.22446852130376</v>
+        <v>40.8</v>
       </c>
       <c r="W7" t="n">
-        <v>41.22446852130376</v>
+        <v>40.8</v>
       </c>
       <c r="X7" t="n">
-        <v>41.22446852130376</v>
+        <v>40.8</v>
       </c>
       <c r="Y7" t="n">
         <v>40.8</v>
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>672.4238518860102</v>
+        <v>269.7141879292489</v>
       </c>
       <c r="C8" t="n">
-        <v>622.4495304284405</v>
+        <v>219.7398664716793</v>
       </c>
       <c r="D8" t="n">
-        <v>612.0059387720266</v>
+        <v>209.2962748152654</v>
       </c>
       <c r="E8" t="n">
-        <v>607.5985755327654</v>
+        <v>204.8889115760041</v>
       </c>
       <c r="F8" t="n">
-        <v>602.6595566357837</v>
+        <v>199.9498926790224</v>
       </c>
       <c r="G8" t="n">
-        <v>441.2866863712601</v>
+        <v>197.2915652585046</v>
       </c>
       <c r="H8" t="n">
-        <v>40.8</v>
+        <v>148.5630108971841</v>
       </c>
       <c r="I8" t="n">
         <v>40.8</v>
@@ -4798,22 +4798,22 @@
         <v>100.6883424103254</v>
       </c>
       <c r="K8" t="n">
-        <v>576.1661551929981</v>
+        <v>242.4406218073104</v>
       </c>
       <c r="L8" t="n">
-        <v>752.0223923789277</v>
+        <v>418.29685899324</v>
       </c>
       <c r="M8" t="n">
-        <v>1256.922392378928</v>
+        <v>923.1968589932401</v>
       </c>
       <c r="N8" t="n">
-        <v>1761.822392378928</v>
+        <v>1428.09685899324</v>
       </c>
       <c r="O8" t="n">
-        <v>1880.036123108616</v>
+        <v>1546.310589722929</v>
       </c>
       <c r="P8" t="n">
-        <v>2040</v>
+        <v>1706.274466614312</v>
       </c>
       <c r="Q8" t="n">
         <v>2040</v>
@@ -4840,7 +4840,7 @@
         <v>867.6932919247788</v>
       </c>
       <c r="Y8" t="n">
-        <v>755.2514407300249</v>
+        <v>352.5417767732636</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>576.0270198522312</v>
+        <v>145.7371093445676</v>
       </c>
       <c r="C9" t="n">
-        <v>576.0270198522312</v>
+        <v>145.7371093445676</v>
       </c>
       <c r="D9" t="n">
-        <v>369.2214865899838</v>
+        <v>145.7371093445676</v>
       </c>
       <c r="E9" t="n">
-        <v>369.2214865899838</v>
+        <v>145.7371093445676</v>
       </c>
       <c r="F9" t="n">
-        <v>369.2214865899838</v>
+        <v>145.7371093445676</v>
       </c>
       <c r="G9" t="n">
         <v>40.8</v>
@@ -4877,49 +4877,49 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K9" t="n">
-        <v>506.3931913728586</v>
+        <v>506.393191372869</v>
       </c>
       <c r="L9" t="n">
-        <v>907.2038982510776</v>
+        <v>907.203898251088</v>
       </c>
       <c r="M9" t="n">
-        <v>1144.358439993937</v>
+        <v>1144.358439993947</v>
       </c>
       <c r="N9" t="n">
-        <v>1432.711203846788</v>
+        <v>1432.711203846799</v>
       </c>
       <c r="O9" t="n">
-        <v>1813.614678172016</v>
+        <v>1813.614678172027</v>
       </c>
       <c r="P9" t="n">
-        <v>2040.000000000014</v>
+        <v>2040.000000000024</v>
       </c>
       <c r="Q9" t="n">
-        <v>2040.000000000014</v>
+        <v>1942.827500480386</v>
       </c>
       <c r="R9" t="n">
-        <v>1929.009505307883</v>
+        <v>1831.837005788255</v>
       </c>
       <c r="S9" t="n">
-        <v>1873.072932063659</v>
+        <v>1831.837005788255</v>
       </c>
       <c r="T9" t="n">
-        <v>1466.072711813455</v>
+        <v>1828.877189578455</v>
       </c>
       <c r="U9" t="n">
-        <v>1466.072711813455</v>
+        <v>1828.704727842417</v>
       </c>
       <c r="V9" t="n">
-        <v>1047.375068185657</v>
+        <v>1410.007084214619</v>
       </c>
       <c r="W9" t="n">
-        <v>1014.674923832294</v>
+        <v>973.2665358208524</v>
       </c>
       <c r="X9" t="n">
-        <v>994.6115506551353</v>
+        <v>549.1627586032891</v>
       </c>
       <c r="Y9" t="n">
-        <v>591.1859013964137</v>
+        <v>145.7371093445676</v>
       </c>
     </row>
     <row r="10">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40.8</v>
+        <v>486.0980900145618</v>
       </c>
       <c r="C11" t="n">
-        <v>40.8</v>
+        <v>486.0980900145618</v>
       </c>
       <c r="D11" t="n">
-        <v>40.8</v>
+        <v>486.0980900145618</v>
       </c>
       <c r="E11" t="n">
-        <v>40.8</v>
+        <v>259.4685045530783</v>
       </c>
       <c r="F11" t="n">
-        <v>40.8</v>
+        <v>259.4685045530783</v>
       </c>
       <c r="G11" t="n">
-        <v>40.8</v>
+        <v>259.4685045530783</v>
       </c>
       <c r="H11" t="n">
         <v>40.8</v>
@@ -5032,25 +5032,25 @@
         <v>40.8</v>
       </c>
       <c r="J11" t="n">
-        <v>526.6900316306205</v>
+        <v>100.6883424103254</v>
       </c>
       <c r="K11" t="n">
-        <v>668.4423110276055</v>
+        <v>242.4406218073104</v>
       </c>
       <c r="L11" t="n">
-        <v>844.2985482135351</v>
+        <v>418.29685899324</v>
       </c>
       <c r="M11" t="n">
-        <v>1349.198548213535</v>
+        <v>923.1968589932401</v>
       </c>
       <c r="N11" t="n">
-        <v>1761.822392378928</v>
+        <v>1256.922392378927</v>
       </c>
       <c r="O11" t="n">
-        <v>1880.036123108616</v>
+        <v>1375.136123108616</v>
       </c>
       <c r="P11" t="n">
-        <v>2040</v>
+        <v>1535.1</v>
       </c>
       <c r="Q11" t="n">
         <v>2040</v>
@@ -5062,22 +5062,22 @@
         <v>1747.708306382961</v>
       </c>
       <c r="T11" t="n">
-        <v>1341.90209977424</v>
+        <v>1747.708306382961</v>
       </c>
       <c r="U11" t="n">
-        <v>1341.90209977424</v>
+        <v>1747.708306382961</v>
       </c>
       <c r="V11" t="n">
-        <v>887.5071258683568</v>
+        <v>1747.708306382961</v>
       </c>
       <c r="W11" t="n">
-        <v>424.5036147764905</v>
+        <v>1542.258270922692</v>
       </c>
       <c r="X11" t="n">
-        <v>424.5036147764905</v>
+        <v>1125.811974497775</v>
       </c>
       <c r="Y11" t="n">
-        <v>89.83954135951433</v>
+        <v>791.1479010807986</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>882.0866135978184</v>
+        <v>735.4833088260165</v>
       </c>
       <c r="C12" t="n">
-        <v>699.1574091073949</v>
+        <v>552.5541043355929</v>
       </c>
       <c r="D12" t="n">
-        <v>529.5233819379982</v>
+        <v>382.9200771661963</v>
       </c>
       <c r="E12" t="n">
-        <v>365.2081322188945</v>
+        <v>218.6048274470926</v>
       </c>
       <c r="F12" t="n">
-        <v>203.9594025846755</v>
+        <v>57.3560978128735</v>
       </c>
       <c r="G12" t="n">
         <v>57.3560978128735</v>
@@ -5114,49 +5114,49 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K12" t="n">
-        <v>506.3931913728777</v>
+        <v>506.3931913728617</v>
       </c>
       <c r="L12" t="n">
-        <v>907.2038982510967</v>
+        <v>907.2038982510808</v>
       </c>
       <c r="M12" t="n">
-        <v>1144.358439993956</v>
+        <v>1144.35843999394</v>
       </c>
       <c r="N12" t="n">
-        <v>1432.711203846807</v>
+        <v>1432.711203846791</v>
       </c>
       <c r="O12" t="n">
-        <v>1813.614678172035</v>
+        <v>1813.614678172019</v>
       </c>
       <c r="P12" t="n">
-        <v>2040.000000000033</v>
+        <v>2040.000000000017</v>
       </c>
       <c r="Q12" t="n">
         <v>2040</v>
       </c>
       <c r="R12" t="n">
-        <v>2030.435860637639</v>
+        <v>2040</v>
       </c>
       <c r="S12" t="n">
-        <v>2030.435860637639</v>
+        <v>2040</v>
       </c>
       <c r="T12" t="n">
-        <v>1805.253822205616</v>
+        <v>1865.273301925053</v>
       </c>
       <c r="U12" t="n">
-        <v>1582.859138247356</v>
+        <v>1642.878617966793</v>
       </c>
       <c r="V12" t="n">
-        <v>1345.97967643774</v>
+        <v>1405.999156157177</v>
       </c>
       <c r="W12" t="n">
-        <v>1345.97967643774</v>
+        <v>1405.999156157177</v>
       </c>
       <c r="X12" t="n">
-        <v>1103.694081038358</v>
+        <v>1163.713560757795</v>
       </c>
       <c r="Y12" t="n">
-        <v>882.0866135978184</v>
+        <v>942.1060933172555</v>
       </c>
     </row>
     <row r="13">
@@ -5166,22 +5166,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="C13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="D13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="E13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="F13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="G13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="H13" t="n">
         <v>40.8</v>
@@ -5196,46 +5196,46 @@
         <v>237.7897671295178</v>
       </c>
       <c r="L13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="M13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="N13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="O13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="P13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="Q13" t="n">
-        <v>106.3753897798654</v>
+        <v>237.7897671295178</v>
       </c>
       <c r="R13" t="n">
-        <v>106.3753897798654</v>
+        <v>151.1046279351681</v>
       </c>
       <c r="S13" t="n">
-        <v>106.3753897798654</v>
+        <v>151.1046279351681</v>
       </c>
       <c r="T13" t="n">
-        <v>78.22671356059527</v>
+        <v>122.9559517158981</v>
       </c>
       <c r="U13" t="n">
-        <v>107.0051717726524</v>
+        <v>151.7344099279552</v>
       </c>
       <c r="V13" t="n">
-        <v>87.64122205930272</v>
+        <v>132.3704602146055</v>
       </c>
       <c r="W13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="X13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
       <c r="Y13" t="n">
-        <v>40.8</v>
+        <v>85.52923815530279</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>341.0310954018805</v>
+        <v>476.0713229002155</v>
       </c>
       <c r="C14" t="n">
-        <v>341.0310954018805</v>
+        <v>476.0713229002155</v>
       </c>
       <c r="D14" t="n">
-        <v>188.1632613212241</v>
+        <v>323.2034888195591</v>
       </c>
       <c r="E14" t="n">
-        <v>188.1632613212241</v>
+        <v>323.2034888195591</v>
       </c>
       <c r="F14" t="n">
-        <v>40.8</v>
+        <v>323.2034888195591</v>
       </c>
       <c r="G14" t="n">
-        <v>40.8</v>
+        <v>179.6705247550985</v>
       </c>
       <c r="H14" t="n">
         <v>40.8</v>
@@ -5272,22 +5272,22 @@
         <v>100.6883424103254</v>
       </c>
       <c r="K14" t="n">
-        <v>576.1661551929981</v>
+        <v>242.4406218073104</v>
       </c>
       <c r="L14" t="n">
-        <v>752.0223923789277</v>
+        <v>418.29685899324</v>
       </c>
       <c r="M14" t="n">
-        <v>1256.922392378928</v>
+        <v>923.1968589932401</v>
       </c>
       <c r="N14" t="n">
-        <v>1761.822392378928</v>
+        <v>1428.09685899324</v>
       </c>
       <c r="O14" t="n">
-        <v>1880.036123108616</v>
+        <v>1546.310589722929</v>
       </c>
       <c r="P14" t="n">
-        <v>2040</v>
+        <v>1706.274466614312</v>
       </c>
       <c r="Q14" t="n">
         <v>2040</v>
@@ -5296,25 +5296,25 @@
         <v>2040</v>
       </c>
       <c r="S14" t="n">
-        <v>1827.678872175716</v>
+        <v>2040</v>
       </c>
       <c r="T14" t="n">
-        <v>1501.670645364974</v>
+        <v>1713.991773189258</v>
       </c>
       <c r="U14" t="n">
-        <v>1107.59867940805</v>
+        <v>1713.991773189258</v>
       </c>
       <c r="V14" t="n">
-        <v>733.0016853001475</v>
+        <v>1339.394779081355</v>
       </c>
       <c r="W14" t="n">
-        <v>349.7961540062611</v>
+        <v>956.189247787469</v>
       </c>
       <c r="X14" t="n">
-        <v>341.0310954018805</v>
+        <v>956.189247787469</v>
       </c>
       <c r="Y14" t="n">
-        <v>341.0310954018805</v>
+        <v>701.3231541684726</v>
       </c>
     </row>
     <row r="15">
@@ -5351,34 +5351,34 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K15" t="n">
-        <v>506.5610117413805</v>
+        <v>506.3931913728599</v>
       </c>
       <c r="L15" t="n">
-        <v>907.3717186195995</v>
+        <v>907.203898251079</v>
       </c>
       <c r="M15" t="n">
-        <v>1144.526260362459</v>
+        <v>1144.358439993938</v>
       </c>
       <c r="N15" t="n">
-        <v>1432.87902421531</v>
+        <v>1432.711203846789</v>
       </c>
       <c r="O15" t="n">
-        <v>1813.614678172044</v>
+        <v>1813.614678172018</v>
       </c>
       <c r="P15" t="n">
-        <v>2040.000000000042</v>
+        <v>2040.000000000015</v>
       </c>
       <c r="Q15" t="n">
-        <v>2040</v>
+        <v>2037.656510527777</v>
       </c>
       <c r="R15" t="n">
-        <v>1786.585262883627</v>
+        <v>1784.241773411404</v>
       </c>
       <c r="S15" t="n">
-        <v>1588.224447215161</v>
+        <v>1585.880957742938</v>
       </c>
       <c r="T15" t="n">
-        <v>1442.840388581118</v>
+        <v>1440.496899108895</v>
       </c>
       <c r="U15" t="n">
         <v>1297.900194948615</v>
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>244.2323830349825</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="C16" t="n">
-        <v>244.2323830349825</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="D16" t="n">
-        <v>217.4281223728053</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="E16" t="n">
-        <v>195.2251881940613</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="F16" t="n">
-        <v>179.6869498428068</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="G16" t="n">
-        <v>194.0033845821511</v>
+        <v>315.6994775587117</v>
       </c>
       <c r="H16" t="n">
-        <v>228.3742582661388</v>
+        <v>350.0703512426994</v>
       </c>
       <c r="I16" t="n">
-        <v>324.9495568743529</v>
+        <v>446.6456498509135</v>
       </c>
       <c r="J16" t="n">
-        <v>581.7840253956566</v>
+        <v>703.4801183722172</v>
       </c>
       <c r="K16" t="n">
-        <v>610.6341314636725</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="L16" t="n">
-        <v>520.2502050251143</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="M16" t="n">
-        <v>335.9235235289138</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="N16" t="n">
-        <v>98.63176013145105</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="O16" t="n">
-        <v>98.63176013145105</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="P16" t="n">
-        <v>98.63176013145105</v>
+        <v>361.2389554052119</v>
       </c>
       <c r="Q16" t="n">
-        <v>98.63176013145105</v>
+        <v>40.8</v>
       </c>
       <c r="R16" t="n">
-        <v>98.63176013145105</v>
+        <v>40.8</v>
       </c>
       <c r="S16" t="n">
         <v>40.8</v>
@@ -5472,7 +5472,7 @@
         <v>301.3830428193674</v>
       </c>
       <c r="Y16" t="n">
-        <v>272.6301611532438</v>
+        <v>301.3830428193674</v>
       </c>
     </row>
     <row r="17">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>132.8787378682305</v>
+        <v>307.251188211549</v>
       </c>
       <c r="C17" t="n">
-        <v>40.8</v>
+        <v>114.852624329737</v>
       </c>
       <c r="D17" t="n">
         <v>40.8</v>
@@ -5506,25 +5506,25 @@
         <v>40.8</v>
       </c>
       <c r="J17" t="n">
-        <v>100.6883424103254</v>
+        <v>526.6900316306205</v>
       </c>
       <c r="K17" t="n">
-        <v>242.4406218073104</v>
+        <v>668.4423110276055</v>
       </c>
       <c r="L17" t="n">
-        <v>418.29685899324</v>
+        <v>1173.342311027606</v>
       </c>
       <c r="M17" t="n">
-        <v>752.0223923789275</v>
+        <v>1678.242311027605</v>
       </c>
       <c r="N17" t="n">
-        <v>1256.922392378927</v>
+        <v>1761.822392378928</v>
       </c>
       <c r="O17" t="n">
-        <v>1375.136123108616</v>
+        <v>1880.036123108616</v>
       </c>
       <c r="P17" t="n">
-        <v>1535.1</v>
+        <v>2040</v>
       </c>
       <c r="Q17" t="n">
         <v>2040</v>
@@ -5533,25 +5533,25 @@
         <v>2040</v>
       </c>
       <c r="S17" t="n">
-        <v>1827.678872175716</v>
+        <v>2040</v>
       </c>
       <c r="T17" t="n">
-        <v>1501.670645364974</v>
+        <v>1713.991773189258</v>
       </c>
       <c r="U17" t="n">
-        <v>1107.59867940805</v>
+        <v>1319.919807232335</v>
       </c>
       <c r="V17" t="n">
-        <v>1107.59867940805</v>
+        <v>945.3228131244318</v>
       </c>
       <c r="W17" t="n">
-        <v>724.393148114164</v>
+        <v>562.1172818305454</v>
       </c>
       <c r="X17" t="n">
-        <v>387.7448314872269</v>
+        <v>562.1172818305454</v>
       </c>
       <c r="Y17" t="n">
-        <v>132.8787378682305</v>
+        <v>307.251188211549</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>536.915907694456</v>
+        <v>534.5724182221533</v>
       </c>
       <c r="C18" t="n">
-        <v>433.7846830020122</v>
+        <v>431.4411935297095</v>
       </c>
       <c r="D18" t="n">
-        <v>343.9486356305954</v>
+        <v>341.6051461582927</v>
       </c>
       <c r="E18" t="n">
-        <v>259.4313657094715</v>
+        <v>257.0878762371688</v>
       </c>
       <c r="F18" t="n">
-        <v>177.9806158732322</v>
+        <v>175.6371264009295</v>
       </c>
       <c r="G18" t="n">
-        <v>111.17529089941</v>
+        <v>108.8318014271073</v>
       </c>
       <c r="H18" t="n">
-        <v>43.14348947230275</v>
+        <v>40.8</v>
       </c>
       <c r="I18" t="n">
         <v>40.8</v>
@@ -5588,49 +5588,49 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K18" t="n">
-        <v>506.3931913729249</v>
+        <v>506.3931913728599</v>
       </c>
       <c r="L18" t="n">
-        <v>907.203898251144</v>
+        <v>907.203898251079</v>
       </c>
       <c r="M18" t="n">
-        <v>1144.358439994003</v>
+        <v>1144.358439993938</v>
       </c>
       <c r="N18" t="n">
-        <v>1432.711203846854</v>
+        <v>1432.711203846789</v>
       </c>
       <c r="O18" t="n">
-        <v>1813.614678172083</v>
+        <v>1813.614678172018</v>
       </c>
       <c r="P18" t="n">
-        <v>2040.00000000008</v>
+        <v>2040.000000000015</v>
       </c>
       <c r="Q18" t="n">
-        <v>2040.00000000008</v>
+        <v>2037.656510527777</v>
       </c>
       <c r="R18" t="n">
-        <v>1786.585262883707</v>
+        <v>1784.241773411404</v>
       </c>
       <c r="S18" t="n">
-        <v>1588.224447215241</v>
+        <v>1585.880957742938</v>
       </c>
       <c r="T18" t="n">
-        <v>1442.840388581198</v>
+        <v>1440.496899108895</v>
       </c>
       <c r="U18" t="n">
-        <v>1300.243684420918</v>
+        <v>1297.900194948615</v>
       </c>
       <c r="V18" t="n">
-        <v>1143.162202409281</v>
+        <v>1140.818712936978</v>
       </c>
       <c r="W18" t="n">
-        <v>968.0378156316767</v>
+        <v>965.694326159374</v>
       </c>
       <c r="X18" t="n">
-        <v>805.5502000302752</v>
+        <v>803.2067105579724</v>
       </c>
       <c r="Y18" t="n">
-        <v>663.7407123877152</v>
+        <v>661.3972229154125</v>
       </c>
     </row>
     <row r="19">
@@ -5643,52 +5643,52 @@
         <v>301.3830428193674</v>
       </c>
       <c r="C19" t="n">
-        <v>287.519157316292</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="D19" t="n">
-        <v>260.7148966541147</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="E19" t="n">
-        <v>238.5119624753708</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="F19" t="n">
-        <v>222.9737241241163</v>
+        <v>301.3830428193674</v>
       </c>
       <c r="G19" t="n">
-        <v>237.2901588634606</v>
+        <v>315.6994775587117</v>
       </c>
       <c r="H19" t="n">
-        <v>271.6610325474483</v>
+        <v>350.0703512426994</v>
       </c>
       <c r="I19" t="n">
-        <v>368.2363311556624</v>
+        <v>446.6456498509135</v>
       </c>
       <c r="J19" t="n">
-        <v>625.0707996769661</v>
+        <v>703.4801183722172</v>
       </c>
       <c r="K19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="L19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="M19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="N19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="O19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="P19" t="n">
-        <v>653.920905744982</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="Q19" t="n">
-        <v>585.722537981858</v>
+        <v>303.4824805759927</v>
       </c>
       <c r="R19" t="n">
-        <v>136.3294297379398</v>
+        <v>40.8</v>
       </c>
       <c r="S19" t="n">
         <v>40.8</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40.8</v>
+        <v>225.4689652036083</v>
       </c>
       <c r="C20" t="n">
-        <v>40.8</v>
+        <v>225.4689652036083</v>
       </c>
       <c r="D20" t="n">
-        <v>40.8</v>
+        <v>225.4689652036083</v>
       </c>
       <c r="E20" t="n">
-        <v>40.8</v>
+        <v>188.1632613212241</v>
       </c>
       <c r="F20" t="n">
         <v>40.8</v>
@@ -5752,16 +5752,16 @@
         <v>844.2985482135351</v>
       </c>
       <c r="M20" t="n">
+        <v>844.2985482135352</v>
+      </c>
+      <c r="N20" t="n">
         <v>1349.198548213535</v>
       </c>
-      <c r="N20" t="n">
-        <v>1761.822392378928</v>
-      </c>
       <c r="O20" t="n">
-        <v>1880.036123108616</v>
+        <v>1854.098548213535</v>
       </c>
       <c r="P20" t="n">
-        <v>2040</v>
+        <v>2014.062425104919</v>
       </c>
       <c r="Q20" t="n">
         <v>2040</v>
@@ -5770,25 +5770,25 @@
         <v>2040</v>
       </c>
       <c r="S20" t="n">
-        <v>1855.331034796392</v>
+        <v>2040</v>
       </c>
       <c r="T20" t="n">
-        <v>1529.32280798565</v>
+        <v>1713.991773189258</v>
       </c>
       <c r="U20" t="n">
-        <v>1135.250842028727</v>
+        <v>1319.919807232335</v>
       </c>
       <c r="V20" t="n">
-        <v>760.6538479208236</v>
+        <v>945.3228131244318</v>
       </c>
       <c r="W20" t="n">
-        <v>377.4483166269371</v>
+        <v>562.1172818305454</v>
       </c>
       <c r="X20" t="n">
-        <v>40.8</v>
+        <v>225.4689652036083</v>
       </c>
       <c r="Y20" t="n">
-        <v>40.8</v>
+        <v>225.4689652036083</v>
       </c>
     </row>
     <row r="21">
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>536.915907694496</v>
+        <v>536.915907694376</v>
       </c>
       <c r="C21" t="n">
-        <v>433.7846830020522</v>
+        <v>433.7846830019322</v>
       </c>
       <c r="D21" t="n">
-        <v>343.9486356306354</v>
+        <v>343.9486356305154</v>
       </c>
       <c r="E21" t="n">
-        <v>259.4313657095115</v>
+        <v>257.0878762371688</v>
       </c>
       <c r="F21" t="n">
-        <v>177.9806158732723</v>
+        <v>175.6371264009295</v>
       </c>
       <c r="G21" t="n">
         <v>108.8318014271073</v>
@@ -5825,49 +5825,49 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K21" t="n">
-        <v>506.393191372965</v>
+        <v>506.3931913728449</v>
       </c>
       <c r="L21" t="n">
-        <v>907.203898251184</v>
+        <v>907.2038982510639</v>
       </c>
       <c r="M21" t="n">
-        <v>1144.358439994043</v>
+        <v>1144.358439993923</v>
       </c>
       <c r="N21" t="n">
-        <v>1432.711203846894</v>
+        <v>1432.711203846774</v>
       </c>
       <c r="O21" t="n">
-        <v>1813.614678172123</v>
+        <v>1813.614678172003</v>
       </c>
       <c r="P21" t="n">
-        <v>2040.00000000012</v>
+        <v>2040</v>
       </c>
       <c r="Q21" t="n">
-        <v>2040.00000000012</v>
+        <v>2040</v>
       </c>
       <c r="R21" t="n">
-        <v>1786.585262883747</v>
+        <v>1786.585262883627</v>
       </c>
       <c r="S21" t="n">
-        <v>1588.224447215281</v>
+        <v>1588.224447215161</v>
       </c>
       <c r="T21" t="n">
-        <v>1442.840388581238</v>
+        <v>1442.840388581118</v>
       </c>
       <c r="U21" t="n">
-        <v>1300.243684420958</v>
+        <v>1300.243684420838</v>
       </c>
       <c r="V21" t="n">
-        <v>1143.162202409321</v>
+        <v>1143.162202409201</v>
       </c>
       <c r="W21" t="n">
-        <v>968.0378156317167</v>
+        <v>968.0378156315967</v>
       </c>
       <c r="X21" t="n">
-        <v>805.5502000303152</v>
+        <v>805.5502000301951</v>
       </c>
       <c r="Y21" t="n">
-        <v>663.7407123877553</v>
+        <v>663.7407123876352</v>
       </c>
     </row>
     <row r="22">
@@ -5910,19 +5910,19 @@
         <v>732.3302244402331</v>
       </c>
       <c r="M22" t="n">
-        <v>548.0035429440327</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="N22" t="n">
-        <v>310.7117795465699</v>
+        <v>732.3302244402331</v>
       </c>
       <c r="O22" t="n">
-        <v>310.7117795465699</v>
+        <v>419.1204312820959</v>
       </c>
       <c r="P22" t="n">
-        <v>310.7117795465699</v>
+        <v>48.02916224707462</v>
       </c>
       <c r="Q22" t="n">
-        <v>310.7117795465699</v>
+        <v>40.8</v>
       </c>
       <c r="R22" t="n">
         <v>40.8</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>301.698872556897</v>
+        <v>40.8</v>
       </c>
       <c r="C23" t="n">
-        <v>109.3003086750849</v>
+        <v>40.8</v>
       </c>
       <c r="D23" t="n">
         <v>40.8</v>
@@ -5983,19 +5983,19 @@
         <v>526.6900316306205</v>
       </c>
       <c r="K23" t="n">
-        <v>1031.59003163062</v>
+        <v>668.4423110276055</v>
       </c>
       <c r="L23" t="n">
-        <v>1207.44626881655</v>
+        <v>844.2985482135351</v>
       </c>
       <c r="M23" t="n">
-        <v>1207.44626881655</v>
+        <v>911.9862692703111</v>
       </c>
       <c r="N23" t="n">
-        <v>1256.922392378927</v>
+        <v>911.9862692703111</v>
       </c>
       <c r="O23" t="n">
-        <v>1375.136123108616</v>
+        <v>1030.2</v>
       </c>
       <c r="P23" t="n">
         <v>1535.1</v>
@@ -6016,16 +6016,16 @@
         <v>1501.670645364974</v>
       </c>
       <c r="V23" t="n">
-        <v>1501.670645364974</v>
+        <v>1240.771772808077</v>
       </c>
       <c r="W23" t="n">
-        <v>1118.465114071088</v>
+        <v>857.5662415141906</v>
       </c>
       <c r="X23" t="n">
-        <v>781.8167974441504</v>
+        <v>520.9179248872534</v>
       </c>
       <c r="Y23" t="n">
-        <v>526.9507038251541</v>
+        <v>266.0518312682571</v>
       </c>
     </row>
     <row r="24">
@@ -6062,25 +6062,25 @@
         <v>221.0882673451103</v>
       </c>
       <c r="K24" t="n">
-        <v>506.5610117413805</v>
+        <v>506.3931913728617</v>
       </c>
       <c r="L24" t="n">
-        <v>907.3717186195995</v>
+        <v>907.2038982510808</v>
       </c>
       <c r="M24" t="n">
-        <v>1144.526260362459</v>
+        <v>1144.35843999394</v>
       </c>
       <c r="N24" t="n">
-        <v>1432.87902421531</v>
+        <v>1432.711203846791</v>
       </c>
       <c r="O24" t="n">
-        <v>1813.614678172003</v>
+        <v>1813.614678172019</v>
       </c>
       <c r="P24" t="n">
-        <v>2040</v>
+        <v>2040.000000000017</v>
       </c>
       <c r="Q24" t="n">
-        <v>2040</v>
+        <v>2037.656510527777</v>
       </c>
       <c r="R24" t="n">
         <v>1784.241773411404</v>
@@ -6153,13 +6153,13 @@
         <v>732.3302244402331</v>
       </c>
       <c r="O25" t="n">
-        <v>732.3302244402331</v>
+        <v>419.1204312820959</v>
       </c>
       <c r="P25" t="n">
-        <v>732.3302244402331</v>
+        <v>419.1204312820959</v>
       </c>
       <c r="Q25" t="n">
-        <v>490.1931082439181</v>
+        <v>40.8</v>
       </c>
       <c r="R25" t="n">
         <v>40.8</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>192.9478787881405</v>
+        <v>192.9478787878788</v>
       </c>
       <c r="C26" t="n">
-        <v>192.9478787881405</v>
+        <v>14.16</v>
       </c>
       <c r="D26" t="n">
-        <v>192.9478787881405</v>
+        <v>14.16</v>
       </c>
       <c r="E26" t="n">
-        <v>192.9478787881405</v>
+        <v>14.16</v>
       </c>
       <c r="F26" t="n">
-        <v>192.9478787881405</v>
+        <v>14.16</v>
       </c>
       <c r="G26" t="n">
-        <v>192.9478787881405</v>
+        <v>14.16</v>
       </c>
       <c r="H26" t="n">
         <v>14.16</v>
@@ -6229,13 +6229,13 @@
         <v>391.0306218073104</v>
       </c>
       <c r="N26" t="n">
-        <v>391.0306218073104</v>
+        <v>429.8223923789276</v>
       </c>
       <c r="O26" t="n">
-        <v>509.244352536999</v>
+        <v>548.0361231086163</v>
       </c>
       <c r="P26" t="n">
-        <v>669.2082294283828</v>
+        <v>708</v>
       </c>
       <c r="Q26" t="n">
         <v>708</v>
@@ -6244,25 +6244,25 @@
         <v>698.7365049143161</v>
       </c>
       <c r="S26" t="n">
-        <v>519.9486261261695</v>
+        <v>698.7365049143161</v>
       </c>
       <c r="T26" t="n">
-        <v>341.1607473380233</v>
+        <v>698.7365049143161</v>
       </c>
       <c r="U26" t="n">
-        <v>341.1607473380233</v>
+        <v>698.7365049143161</v>
       </c>
       <c r="V26" t="n">
-        <v>192.9478787881405</v>
+        <v>698.7365049143161</v>
       </c>
       <c r="W26" t="n">
-        <v>192.9478787881405</v>
+        <v>698.7365049143161</v>
       </c>
       <c r="X26" t="n">
-        <v>192.9478787881405</v>
+        <v>550.5236363636363</v>
       </c>
       <c r="Y26" t="n">
-        <v>192.9478787881405</v>
+        <v>371.7357575757576</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>196.7276972197788</v>
+        <v>562.2777406992293</v>
       </c>
       <c r="C27" t="n">
-        <v>196.7276972197788</v>
+        <v>562.2777406992293</v>
       </c>
       <c r="D27" t="n">
-        <v>196.7276972197788</v>
+        <v>383.5528044389235</v>
       </c>
       <c r="E27" t="n">
-        <v>196.7276972197788</v>
+        <v>210.1466456289108</v>
       </c>
       <c r="F27" t="n">
-        <v>196.7276972197788</v>
+        <v>39.80700690378259</v>
       </c>
       <c r="G27" t="n">
-        <v>196.7276972197788</v>
+        <v>39.80700690378259</v>
       </c>
       <c r="H27" t="n">
         <v>39.80700690378259</v>
@@ -6305,13 +6305,13 @@
         <v>381.2222637830189</v>
       </c>
       <c r="M27" t="n">
-        <v>381.2222637830189</v>
+        <v>556.4522637830189</v>
       </c>
       <c r="N27" t="n">
-        <v>530.7215064876663</v>
+        <v>696.5253893818129</v>
       </c>
       <c r="O27" t="n">
-        <v>532.77</v>
+        <v>698.5738828941467</v>
       </c>
       <c r="P27" t="n">
         <v>708</v>
@@ -6320,28 +6320,28 @@
         <v>708</v>
       </c>
       <c r="R27" t="n">
-        <v>554.3034547960315</v>
+        <v>708</v>
       </c>
       <c r="S27" t="n">
-        <v>554.3034547960315</v>
+        <v>708</v>
       </c>
       <c r="T27" t="n">
-        <v>375.5155760078896</v>
+        <v>708</v>
       </c>
       <c r="U27" t="n">
-        <v>375.5155760078896</v>
+        <v>708</v>
       </c>
       <c r="V27" t="n">
-        <v>375.5155760078896</v>
+        <v>708</v>
       </c>
       <c r="W27" t="n">
-        <v>196.7276972197788</v>
+        <v>562.2777406992293</v>
       </c>
       <c r="X27" t="n">
-        <v>196.7276972197788</v>
+        <v>562.2777406992293</v>
       </c>
       <c r="Y27" t="n">
-        <v>196.7276972197788</v>
+        <v>562.2777406992293</v>
       </c>
     </row>
     <row r="28">
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>175.9586400313958</v>
+        <v>14.16</v>
       </c>
       <c r="C28" t="n">
-        <v>175.9586400313958</v>
+        <v>14.16</v>
       </c>
       <c r="D28" t="n">
-        <v>175.9586400313958</v>
+        <v>14.16</v>
       </c>
       <c r="E28" t="n">
-        <v>64.86681696376289</v>
+        <v>14.16</v>
       </c>
       <c r="F28" t="n">
         <v>14.16</v>
@@ -6372,7 +6372,7 @@
         <v>14.16</v>
       </c>
       <c r="I28" t="n">
-        <v>23.61529860821406</v>
+        <v>23.61529860821405</v>
       </c>
       <c r="J28" t="n">
         <v>193.3297671295178</v>
@@ -6405,22 +6405,22 @@
         <v>193.3297671295178</v>
       </c>
       <c r="T28" t="n">
-        <v>156.0901818193386</v>
+        <v>193.3297671295178</v>
       </c>
       <c r="U28" t="n">
-        <v>175.9586400313958</v>
+        <v>213.198225341575</v>
       </c>
       <c r="V28" t="n">
-        <v>175.9586400313958</v>
+        <v>184.7433665373162</v>
       </c>
       <c r="W28" t="n">
-        <v>175.9586400313958</v>
+        <v>128.8112353871044</v>
       </c>
       <c r="X28" t="n">
-        <v>175.9586400313958</v>
+        <v>128.8112353871044</v>
       </c>
       <c r="Y28" t="n">
-        <v>175.9586400313958</v>
+        <v>128.8112353871044</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="C29" t="n">
-        <v>373.8359595960165</v>
+        <v>712</v>
       </c>
       <c r="D29" t="n">
-        <v>194.0379797980083</v>
+        <v>712</v>
       </c>
       <c r="E29" t="n">
-        <v>194.0379797980083</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="F29" t="n">
-        <v>14.24</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="G29" t="n">
-        <v>14.24</v>
+        <v>194.0379797979798</v>
       </c>
       <c r="H29" t="n">
         <v>14.24</v>
@@ -6460,7 +6460,7 @@
         <v>215.8806218073103</v>
       </c>
       <c r="L29" t="n">
-        <v>391.73685899324</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="M29" t="n">
         <v>433.8223923789276</v>
@@ -6484,22 +6484,22 @@
         <v>712</v>
       </c>
       <c r="T29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="U29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="V29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="W29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="X29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
       <c r="Y29" t="n">
-        <v>532.2020202019918</v>
+        <v>712</v>
       </c>
     </row>
     <row r="30">
@@ -6509,37 +6509,37 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="C30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="D30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="E30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="F30" t="n">
-        <v>300.9867595673384</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="G30" t="n">
-        <v>162.4642628763444</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="H30" t="n">
-        <v>22.71528973206541</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="I30" t="n">
         <v>14.24</v>
       </c>
       <c r="J30" t="n">
-        <v>171.8653893818129</v>
+        <v>190.46</v>
       </c>
       <c r="K30" t="n">
-        <v>348.0853893818129</v>
+        <v>366.68</v>
       </c>
       <c r="L30" t="n">
-        <v>524.3053893818129</v>
+        <v>542.9</v>
       </c>
       <c r="M30" t="n">
         <v>700.5253893818129</v>
@@ -6557,28 +6557,28 @@
         <v>712</v>
       </c>
       <c r="R30" t="n">
-        <v>633.9526609187292</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="S30" t="n">
-        <v>633.9526609187292</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="T30" t="n">
-        <v>633.9526609187292</v>
+        <v>382.311249328025</v>
       </c>
       <c r="U30" t="n">
-        <v>454.1546811207494</v>
+        <v>382.311249328025</v>
       </c>
       <c r="V30" t="n">
-        <v>454.1546811207494</v>
+        <v>382.311249328025</v>
       </c>
       <c r="W30" t="n">
-        <v>454.1546811207494</v>
+        <v>202.5132695300452</v>
       </c>
       <c r="X30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="Y30" t="n">
-        <v>454.1546811207494</v>
+        <v>22.71528973206542</v>
       </c>
     </row>
     <row r="31">
@@ -6588,22 +6588,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>149.4098624538437</v>
+        <v>52.85875360154289</v>
       </c>
       <c r="C31" t="n">
-        <v>149.4098624538437</v>
+        <v>14.24</v>
       </c>
       <c r="D31" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="E31" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="F31" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="G31" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="H31" t="n">
         <v>14.24</v>
@@ -6642,22 +6642,22 @@
         <v>216.7452986082141</v>
       </c>
       <c r="T31" t="n">
-        <v>196.677430469752</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="U31" t="n">
-        <v>233.3758886818092</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="V31" t="n">
-        <v>222.0927470492676</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="W31" t="n">
-        <v>183.3323330707729</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="X31" t="n">
-        <v>183.3323330707729</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="Y31" t="n">
-        <v>149.4098624538437</v>
+        <v>152.9737034369759</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="C32" t="n">
-        <v>553.6339393940327</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="D32" t="n">
-        <v>373.8359595960218</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="E32" t="n">
-        <v>194.0379797980109</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="F32" t="n">
-        <v>14.24</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="G32" t="n">
-        <v>14.24</v>
+        <v>194.0379797979798</v>
       </c>
       <c r="H32" t="n">
         <v>14.24</v>
@@ -6697,19 +6697,19 @@
         <v>215.8806218073103</v>
       </c>
       <c r="L32" t="n">
-        <v>391.7368589932421</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="M32" t="n">
-        <v>433.8223923789276</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="N32" t="n">
-        <v>433.8223923789276</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="O32" t="n">
-        <v>552.0361231086163</v>
+        <v>509.950589722934</v>
       </c>
       <c r="P32" t="n">
-        <v>712</v>
+        <v>669.9144666143177</v>
       </c>
       <c r="Q32" t="n">
         <v>712</v>
@@ -6724,19 +6724,19 @@
         <v>712</v>
       </c>
       <c r="U32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="V32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="W32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="X32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="Y32" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
     </row>
     <row r="33">
@@ -6746,46 +6746,46 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="C33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="D33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="E33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="F33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="G33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="H33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="I33" t="n">
         <v>14.24</v>
       </c>
       <c r="J33" t="n">
-        <v>14.24</v>
+        <v>190.46</v>
       </c>
       <c r="K33" t="n">
-        <v>190.46</v>
+        <v>366.68</v>
       </c>
       <c r="L33" t="n">
-        <v>359.5599999999999</v>
+        <v>524.3053893818129</v>
       </c>
       <c r="M33" t="n">
-        <v>359.5599999999999</v>
+        <v>524.3053893818129</v>
       </c>
       <c r="N33" t="n">
-        <v>359.5599999999999</v>
+        <v>700.5253893818129</v>
       </c>
       <c r="O33" t="n">
-        <v>535.78</v>
+        <v>702.5738828941467</v>
       </c>
       <c r="P33" t="n">
         <v>712</v>
@@ -6794,28 +6794,28 @@
         <v>712</v>
       </c>
       <c r="R33" t="n">
-        <v>712</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="S33" t="n">
-        <v>562.1092291260048</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="T33" t="n">
-        <v>382.311249328025</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="U33" t="n">
-        <v>382.311249328025</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="V33" t="n">
-        <v>202.5132695300452</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="W33" t="n">
-        <v>202.5132695300452</v>
+        <v>194.0379797979798</v>
       </c>
       <c r="X33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
       <c r="Y33" t="n">
-        <v>22.71528973206541</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="34">
@@ -6867,34 +6867,34 @@
         <v>216.7452986082141</v>
       </c>
       <c r="P34" t="n">
-        <v>216.7452986082141</v>
+        <v>84.30139561193583</v>
       </c>
       <c r="Q34" t="n">
-        <v>216.7452986082141</v>
+        <v>84.30139561193583</v>
       </c>
       <c r="R34" t="n">
-        <v>216.7452986082141</v>
+        <v>84.30139561193583</v>
       </c>
       <c r="S34" t="n">
-        <v>216.7452986082141</v>
+        <v>84.30139561193583</v>
       </c>
       <c r="T34" t="n">
-        <v>196.677430469752</v>
+        <v>64.23352747347383</v>
       </c>
       <c r="U34" t="n">
-        <v>233.3758886818092</v>
+        <v>100.931985685531</v>
       </c>
       <c r="V34" t="n">
-        <v>222.0927470492676</v>
+        <v>89.64884405298935</v>
       </c>
       <c r="W34" t="n">
-        <v>183.3323330707729</v>
+        <v>50.88843007449472</v>
       </c>
       <c r="X34" t="n">
-        <v>183.3323330707729</v>
+        <v>50.88843007449472</v>
       </c>
       <c r="Y34" t="n">
-        <v>151.0033799099277</v>
+        <v>50.88843007449472</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
       <c r="C35" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
       <c r="D35" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
       <c r="E35" t="n">
-        <v>14.24</v>
+        <v>553.6339393939395</v>
       </c>
       <c r="F35" t="n">
-        <v>14.24</v>
+        <v>373.8359595959597</v>
       </c>
       <c r="G35" t="n">
-        <v>14.24</v>
+        <v>194.0379797979798</v>
       </c>
       <c r="H35" t="n">
         <v>14.24</v>
@@ -6934,19 +6934,19 @@
         <v>215.8806218073103</v>
       </c>
       <c r="L35" t="n">
-        <v>391.7368589932427</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="M35" t="n">
-        <v>391.7368589932428</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="N35" t="n">
-        <v>433.8223923789276</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="O35" t="n">
-        <v>552.0361231086163</v>
+        <v>509.950589722934</v>
       </c>
       <c r="P35" t="n">
-        <v>712</v>
+        <v>669.9144666143177</v>
       </c>
       <c r="Q35" t="n">
         <v>712</v>
@@ -6955,25 +6955,25 @@
         <v>712</v>
       </c>
       <c r="S35" t="n">
-        <v>532.2020202019626</v>
+        <v>712</v>
       </c>
       <c r="T35" t="n">
-        <v>532.2020202019626</v>
+        <v>712</v>
       </c>
       <c r="U35" t="n">
-        <v>532.2020202019626</v>
+        <v>712</v>
       </c>
       <c r="V35" t="n">
-        <v>352.4040404039251</v>
+        <v>712</v>
       </c>
       <c r="W35" t="n">
-        <v>172.6060606058876</v>
+        <v>712</v>
       </c>
       <c r="X35" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
       <c r="Y35" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22.71528973206541</v>
+        <v>475.8351559769538</v>
       </c>
       <c r="C36" t="n">
-        <v>22.71528973206541</v>
+        <v>300.9867595673384</v>
       </c>
       <c r="D36" t="n">
-        <v>22.71528973206541</v>
+        <v>300.9867595673384</v>
       </c>
       <c r="E36" t="n">
-        <v>22.71528973206541</v>
+        <v>300.9867595673384</v>
       </c>
       <c r="F36" t="n">
-        <v>22.71528973206541</v>
+        <v>300.9867595673384</v>
       </c>
       <c r="G36" t="n">
-        <v>22.71528973206541</v>
+        <v>162.4642628763444</v>
       </c>
       <c r="H36" t="n">
         <v>22.71528973206541</v>
@@ -7007,19 +7007,19 @@
         <v>14.24</v>
       </c>
       <c r="J36" t="n">
-        <v>190.46</v>
+        <v>14.24</v>
       </c>
       <c r="K36" t="n">
-        <v>366.68</v>
+        <v>171.8653893818129</v>
       </c>
       <c r="L36" t="n">
-        <v>383.2822637830189</v>
+        <v>348.0853893818129</v>
       </c>
       <c r="M36" t="n">
-        <v>383.2822637830189</v>
+        <v>524.3053893818129</v>
       </c>
       <c r="N36" t="n">
-        <v>526.3538828941466</v>
+        <v>700.5253893818129</v>
       </c>
       <c r="O36" t="n">
         <v>702.5738828941467</v>
@@ -7031,28 +7031,28 @@
         <v>712</v>
       </c>
       <c r="R36" t="n">
-        <v>712</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="S36" t="n">
-        <v>712</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="T36" t="n">
-        <v>712</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="U36" t="n">
         <v>532.2020202020202</v>
       </c>
       <c r="V36" t="n">
-        <v>352.4040404040404</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="W36" t="n">
-        <v>352.4040404040404</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="X36" t="n">
-        <v>352.4040404040404</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="Y36" t="n">
-        <v>202.5132695300452</v>
+        <v>532.2020202020202</v>
       </c>
     </row>
     <row r="37">
@@ -7062,22 +7062,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>141.0510414352418</v>
+        <v>14.24</v>
       </c>
       <c r="C37" t="n">
-        <v>141.0510414352418</v>
+        <v>14.24</v>
       </c>
       <c r="D37" t="n">
-        <v>141.0510414352418</v>
+        <v>14.24</v>
       </c>
       <c r="E37" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="F37" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="G37" t="n">
-        <v>50.88843007449472</v>
+        <v>14.24</v>
       </c>
       <c r="H37" t="n">
         <v>14.24</v>
@@ -7128,10 +7128,10 @@
         <v>141.0510414352418</v>
       </c>
       <c r="X37" t="n">
-        <v>141.0510414352418</v>
+        <v>81.00695514220385</v>
       </c>
       <c r="Y37" t="n">
-        <v>141.0510414352418</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.24</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="C38" t="n">
-        <v>14.24</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="D38" t="n">
-        <v>14.24</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="E38" t="n">
-        <v>14.24</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="F38" t="n">
-        <v>14.24</v>
+        <v>352.4040404040404</v>
       </c>
       <c r="G38" t="n">
-        <v>14.24</v>
+        <v>194.0379797979798</v>
       </c>
       <c r="H38" t="n">
         <v>14.24</v>
@@ -7171,10 +7171,10 @@
         <v>215.8806218073103</v>
       </c>
       <c r="L38" t="n">
-        <v>391.73685899324</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="M38" t="n">
-        <v>433.8223923789276</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="N38" t="n">
         <v>433.8223923789276</v>
@@ -7198,19 +7198,19 @@
         <v>712</v>
       </c>
       <c r="U38" t="n">
-        <v>553.6339393941435</v>
+        <v>712</v>
       </c>
       <c r="V38" t="n">
-        <v>373.8359595960957</v>
+        <v>712</v>
       </c>
       <c r="W38" t="n">
-        <v>194.0379797980478</v>
+        <v>712</v>
       </c>
       <c r="X38" t="n">
-        <v>14.24</v>
+        <v>712</v>
       </c>
       <c r="Y38" t="n">
-        <v>14.24</v>
+        <v>532.2020202020202</v>
       </c>
     </row>
     <row r="39">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>352.4040404040404</v>
+        <v>197.5636861416809</v>
       </c>
       <c r="C39" t="n">
-        <v>177.555643994425</v>
+        <v>22.71528973206542</v>
       </c>
       <c r="D39" t="n">
         <v>22.71528973206542</v>
@@ -7247,19 +7247,19 @@
         <v>14.24</v>
       </c>
       <c r="K39" t="n">
-        <v>14.24</v>
+        <v>190.46</v>
       </c>
       <c r="L39" t="n">
-        <v>183.3399999999999</v>
+        <v>350.1338828941466</v>
       </c>
       <c r="M39" t="n">
-        <v>183.3399999999999</v>
+        <v>350.1338828941466</v>
       </c>
       <c r="N39" t="n">
-        <v>359.5599999999999</v>
+        <v>526.3538828941466</v>
       </c>
       <c r="O39" t="n">
-        <v>535.78</v>
+        <v>702.5738828941467</v>
       </c>
       <c r="P39" t="n">
         <v>712</v>
@@ -7268,28 +7268,28 @@
         <v>712</v>
       </c>
       <c r="R39" t="n">
-        <v>532.2020202020202</v>
+        <v>712</v>
       </c>
       <c r="S39" t="n">
-        <v>532.2020202020202</v>
+        <v>712</v>
       </c>
       <c r="T39" t="n">
-        <v>532.2020202020202</v>
+        <v>712</v>
       </c>
       <c r="U39" t="n">
-        <v>532.2020202020202</v>
+        <v>712</v>
       </c>
       <c r="V39" t="n">
-        <v>532.2020202020202</v>
+        <v>557.1596457376405</v>
       </c>
       <c r="W39" t="n">
-        <v>532.2020202020202</v>
+        <v>557.1596457376405</v>
       </c>
       <c r="X39" t="n">
-        <v>532.2020202020202</v>
+        <v>377.3616659396607</v>
       </c>
       <c r="Y39" t="n">
-        <v>532.2020202020202</v>
+        <v>377.3616659396607</v>
       </c>
     </row>
     <row r="40">
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>141.0510414352418</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="C40" t="n">
-        <v>141.0510414352418</v>
+        <v>206.6815382752647</v>
       </c>
       <c r="D40" t="n">
-        <v>141.0510414352418</v>
+        <v>108.1601058959157</v>
       </c>
       <c r="E40" t="n">
-        <v>141.0510414352418</v>
+        <v>14.24</v>
       </c>
       <c r="F40" t="n">
-        <v>53.79563136681561</v>
+        <v>14.24</v>
       </c>
       <c r="G40" t="n">
-        <v>50.88843007449471</v>
+        <v>14.24</v>
       </c>
       <c r="H40" t="n">
         <v>14.24</v>
@@ -7326,49 +7326,49 @@
         <v>216.7452986082141</v>
       </c>
       <c r="K40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="L40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="M40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="N40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="O40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="P40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="Q40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="R40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="S40" t="n">
-        <v>174.4640069726829</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="T40" t="n">
-        <v>154.3961388342209</v>
+        <v>216.7452986082141</v>
       </c>
       <c r="U40" t="n">
-        <v>191.094597046278</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="V40" t="n">
-        <v>179.8114554137364</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="W40" t="n">
-        <v>141.0510414352418</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="X40" t="n">
-        <v>141.0510414352418</v>
+        <v>253.4437568202712</v>
       </c>
       <c r="Y40" t="n">
-        <v>141.0510414352418</v>
+        <v>253.4437568202712</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>204.8312937255798</v>
+        <v>712</v>
       </c>
       <c r="C41" t="n">
-        <v>204.8312937255798</v>
+        <v>564.4272533214265</v>
       </c>
       <c r="D41" t="n">
-        <v>25.03331392748713</v>
+        <v>384.6292735234467</v>
       </c>
       <c r="E41" t="n">
-        <v>25.03331392748713</v>
+        <v>384.6292735234467</v>
       </c>
       <c r="F41" t="n">
-        <v>25.03331392748713</v>
+        <v>384.6292735234467</v>
       </c>
       <c r="G41" t="n">
-        <v>25.03331392748713</v>
+        <v>204.8312937254669</v>
       </c>
       <c r="H41" t="n">
         <v>25.03331392748713</v>
@@ -7408,10 +7408,10 @@
         <v>215.8806218073103</v>
       </c>
       <c r="L41" t="n">
-        <v>391.73685899324</v>
+        <v>391.7368589932453</v>
       </c>
       <c r="M41" t="n">
-        <v>391.73685899324</v>
+        <v>433.8223923789276</v>
       </c>
       <c r="N41" t="n">
         <v>433.8223923789276</v>
@@ -7426,28 +7426,28 @@
         <v>712</v>
       </c>
       <c r="R41" t="n">
-        <v>626.9789291567404</v>
+        <v>712</v>
       </c>
       <c r="S41" t="n">
-        <v>626.9789291567404</v>
+        <v>712</v>
       </c>
       <c r="T41" t="n">
-        <v>447.1809493586477</v>
+        <v>712</v>
       </c>
       <c r="U41" t="n">
-        <v>447.1809493586477</v>
+        <v>712</v>
       </c>
       <c r="V41" t="n">
-        <v>447.1809493586477</v>
+        <v>712</v>
       </c>
       <c r="W41" t="n">
-        <v>447.1809493586477</v>
+        <v>712</v>
       </c>
       <c r="X41" t="n">
-        <v>267.382969560555</v>
+        <v>712</v>
       </c>
       <c r="Y41" t="n">
-        <v>267.382969560555</v>
+        <v>712</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>295.4425624593382</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="C42" t="n">
-        <v>295.4425624593382</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="D42" t="n">
-        <v>295.4425624593382</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="E42" t="n">
-        <v>295.4425624593382</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="F42" t="n">
         <v>115.6445826613584</v>
@@ -7481,22 +7481,22 @@
         <v>14.24</v>
       </c>
       <c r="J42" t="n">
-        <v>14.24</v>
+        <v>190.46</v>
       </c>
       <c r="K42" t="n">
         <v>190.46</v>
       </c>
       <c r="L42" t="n">
-        <v>350.1338828941466</v>
+        <v>207.0622637830189</v>
       </c>
       <c r="M42" t="n">
-        <v>350.1338828941466</v>
+        <v>383.2822637830189</v>
       </c>
       <c r="N42" t="n">
-        <v>526.3538828941466</v>
+        <v>533.7315064876663</v>
       </c>
       <c r="O42" t="n">
-        <v>702.5738828941467</v>
+        <v>535.78</v>
       </c>
       <c r="P42" t="n">
         <v>712</v>
@@ -7508,25 +7508,25 @@
         <v>711.7971974500588</v>
       </c>
       <c r="S42" t="n">
-        <v>711.7971974500588</v>
+        <v>655.0385220552978</v>
       </c>
       <c r="T42" t="n">
-        <v>711.7971974500588</v>
+        <v>475.240542257318</v>
       </c>
       <c r="U42" t="n">
-        <v>711.7971974500588</v>
+        <v>295.4425624593382</v>
       </c>
       <c r="V42" t="n">
-        <v>531.999217652079</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="W42" t="n">
-        <v>531.999217652079</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="X42" t="n">
-        <v>352.2012378540992</v>
+        <v>115.6445826613584</v>
       </c>
       <c r="Y42" t="n">
-        <v>295.4425624593382</v>
+        <v>115.6445826613584</v>
       </c>
     </row>
     <row r="43">
@@ -7554,7 +7554,7 @@
         <v>54.21876115680742</v>
       </c>
       <c r="H43" t="n">
-        <v>54.21876115680742</v>
+        <v>14.24</v>
       </c>
       <c r="I43" t="n">
         <v>14.24</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>301.8009906953237</v>
+        <v>481.5989704931437</v>
       </c>
       <c r="C44" t="n">
-        <v>301.8009906953237</v>
+        <v>481.5989704931437</v>
       </c>
       <c r="D44" t="n">
-        <v>301.8009906953237</v>
+        <v>481.5989704931437</v>
       </c>
       <c r="E44" t="n">
-        <v>301.8009906953237</v>
+        <v>481.5989704931437</v>
       </c>
       <c r="F44" t="n">
-        <v>301.8009906953237</v>
+        <v>301.8009906951639</v>
       </c>
       <c r="G44" t="n">
-        <v>301.8009906953237</v>
+        <v>122.0030108971841</v>
       </c>
       <c r="H44" t="n">
         <v>122.0030108971841</v>
@@ -7648,43 +7648,43 @@
         <v>391.73685899324</v>
       </c>
       <c r="M44" t="n">
-        <v>391.73685899324</v>
+        <v>433.8223923789276</v>
       </c>
       <c r="N44" t="n">
-        <v>391.73685899324</v>
+        <v>433.8223923789276</v>
       </c>
       <c r="O44" t="n">
-        <v>509.9505897229287</v>
+        <v>552.0361231086163</v>
       </c>
       <c r="P44" t="n">
-        <v>669.9144666143125</v>
+        <v>712</v>
       </c>
       <c r="Q44" t="n">
         <v>712</v>
       </c>
       <c r="R44" t="n">
-        <v>532.2020202018605</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="S44" t="n">
-        <v>532.2020202018605</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="T44" t="n">
-        <v>532.2020202018605</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="U44" t="n">
-        <v>532.2020202018605</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="V44" t="n">
-        <v>481.5989704934632</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="W44" t="n">
-        <v>481.5989704934632</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="X44" t="n">
-        <v>301.8009906953237</v>
+        <v>532.2020202020202</v>
       </c>
       <c r="Y44" t="n">
-        <v>301.8009906953237</v>
+        <v>532.2020202020202</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="C45" t="n">
         <v>435.029520682382</v>
@@ -7712,7 +7712,7 @@
         <v>194.0379797979798</v>
       </c>
       <c r="H45" t="n">
-        <v>194.0379797979798</v>
+        <v>14.24</v>
       </c>
       <c r="I45" t="n">
         <v>14.24</v>
@@ -7721,13 +7721,13 @@
         <v>14.24</v>
       </c>
       <c r="K45" t="n">
-        <v>190.46</v>
+        <v>166.7377362169811</v>
       </c>
       <c r="L45" t="n">
-        <v>207.0622637830189</v>
+        <v>183.3399999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>207.0622637830189</v>
+        <v>183.3399999999999</v>
       </c>
       <c r="N45" t="n">
         <v>359.5599999999999</v>
@@ -7745,25 +7745,25 @@
         <v>614.8275004803618</v>
       </c>
       <c r="S45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="T45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="U45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="V45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="W45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="X45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
       <c r="Y45" t="n">
-        <v>435.029520682382</v>
+        <v>614.8275004803618</v>
       </c>
     </row>
     <row r="46">
@@ -7827,7 +7827,7 @@
         <v>14.66446852130376</v>
       </c>
       <c r="T46" t="n">
-        <v>14.66446852130376</v>
+        <v>14.24</v>
       </c>
       <c r="U46" t="n">
         <v>14.24</v>
@@ -7967,13 +7967,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>337.0964983693815</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>856.6116753810109</v>
+        <v>683.708173750392</v>
       </c>
       <c r="N2" t="n">
         <v>786.4003148537548</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>51.26750844808842</v>
+        <v>561.2675084480884</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,16 +8210,16 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>346.6116753810107</v>
+        <v>763.4034371642352</v>
       </c>
       <c r="N5" t="n">
-        <v>344.7717502646396</v>
+        <v>276.4003148537548</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>348.4203263723397</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>561.2675084480884</v>
@@ -8283,13 +8283,13 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K6" t="n">
-        <v>295.7107253392402</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
         <v>388.0893364597981</v>
       </c>
       <c r="M6" t="n">
-        <v>471.6948204301074</v>
+        <v>471.5253049063342</v>
       </c>
       <c r="N6" t="n">
         <v>485.4085271713503</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>337.0964983693815</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.26750844808842</v>
+        <v>388.3640068174699</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8520,7 +8520,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>295.7107253392539</v>
+        <v>295.7107253392645</v>
       </c>
       <c r="L9" t="n">
         <v>388.0893364597981</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>856.6116753810109</v>
       </c>
       <c r="N11" t="n">
-        <v>693.1920766369797</v>
+        <v>613.4968132231361</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>51.26750844808842</v>
+        <v>561.2675084480884</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8757,7 +8757,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>295.7107253392733</v>
+        <v>295.7107253392572</v>
       </c>
       <c r="L12" t="n">
         <v>388.0893364597981</v>
@@ -8915,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>337.0964983693815</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>51.26750844808842</v>
+        <v>388.3640068174699</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -8994,7 +8994,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K15" t="n">
-        <v>295.8802408630135</v>
+        <v>295.7107253392554</v>
       </c>
       <c r="L15" t="n">
         <v>388.0893364597981</v>
@@ -9006,7 +9006,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>382.5122832771726</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P15" t="n">
         <v>219.1507118405495</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>332.3674371859296</v>
       </c>
       <c r="M17" t="n">
-        <v>683.708173750392</v>
+        <v>856.6116753810109</v>
       </c>
       <c r="N17" t="n">
-        <v>786.4003148537548</v>
+        <v>360.82463945105</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>561.2675084480884</v>
+        <v>51.26750844808842</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9231,7 +9231,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K18" t="n">
-        <v>295.710725339321</v>
+        <v>295.7107253392554</v>
       </c>
       <c r="L18" t="n">
         <v>388.0893364597981</v>
@@ -9395,19 +9395,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>856.6116753810109</v>
+        <v>346.6116753810107</v>
       </c>
       <c r="N20" t="n">
-        <v>693.1920766369797</v>
+        <v>786.4003148537548</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>390.5921911821326</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>51.26750844808842</v>
+        <v>77.46707904918041</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9468,7 +9468,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K21" t="n">
-        <v>295.7107253393615</v>
+        <v>295.7107253392402</v>
       </c>
       <c r="L21" t="n">
         <v>388.0893364597981</v>
@@ -9626,22 +9626,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>366.8158793969849</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>346.6116753810107</v>
+        <v>414.9831107918955</v>
       </c>
       <c r="N23" t="n">
-        <v>326.3761972399946</v>
+        <v>276.4003148537548</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>348.4203263723397</v>
       </c>
       <c r="Q23" t="n">
         <v>561.2675084480884</v>
@@ -9705,7 +9705,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K24" t="n">
-        <v>295.8802408630135</v>
+        <v>295.7107253392572</v>
       </c>
       <c r="L24" t="n">
         <v>388.0893364597981</v>
@@ -9717,7 +9717,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.5122832771303</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9872,7 +9872,7 @@
         <v>346.6116753810107</v>
       </c>
       <c r="N26" t="n">
-        <v>276.4003148537548</v>
+        <v>315.5839214917521</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>90.45111508608562</v>
+        <v>51.26750844808842</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9948,16 +9948,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>232.1447782656032</v>
+        <v>409.1447782656032</v>
       </c>
       <c r="N27" t="n">
-        <v>345.1524452034675</v>
+        <v>335.6311147935146</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>167.4786695900472</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>389.1223151645335</v>
+        <v>389.1223151645282</v>
       </c>
       <c r="N29" t="n">
         <v>276.4003148537548</v>
@@ -10176,7 +10176,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
-        <v>204.5729460052658</v>
+        <v>223.3553809731316</v>
       </c>
       <c r="K30" t="n">
         <v>185.5239333920335</v>
@@ -10185,7 +10185,7 @@
         <v>161.2300365828092</v>
       </c>
       <c r="M30" t="n">
-        <v>410.1447782656032</v>
+        <v>391.3623432977375</v>
       </c>
       <c r="N30" t="n">
         <v>194.1431091381671</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>389.1223151645314</v>
+        <v>346.6116753810107</v>
       </c>
       <c r="N32" t="n">
         <v>276.4003148537548</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>51.26750844808842</v>
+        <v>93.77814823160591</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10413,25 +10413,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>45.35538097313157</v>
+        <v>223.3553809731316</v>
       </c>
       <c r="K33" t="n">
         <v>185.5239333920335</v>
       </c>
       <c r="L33" t="n">
-        <v>154.0381173908899</v>
+        <v>142.4476016149435</v>
       </c>
       <c r="M33" t="n">
         <v>232.1447782656032</v>
       </c>
       <c r="N33" t="n">
-        <v>194.1431091381671</v>
+        <v>372.1431091381671</v>
       </c>
       <c r="O33" t="n">
-        <v>175.9308146340064</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>168.4786695900472</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10583,7 +10583,7 @@
         <v>346.6116753810107</v>
       </c>
       <c r="N35" t="n">
-        <v>318.9109546372748</v>
+        <v>276.4003148537548</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>51.26750844808842</v>
+        <v>93.77814823160591</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,22 +10650,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>223.3553809731316</v>
+        <v>45.35538097313157</v>
       </c>
       <c r="K36" t="n">
-        <v>185.5239333920335</v>
+        <v>166.7414984241677</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>161.2300365828092</v>
       </c>
       <c r="M36" t="n">
-        <v>232.1447782656032</v>
+        <v>410.1447782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>338.6598961191042</v>
+        <v>372.1431091381671</v>
       </c>
       <c r="O36" t="n">
-        <v>175.9308146340064</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>389.1223151645335</v>
+        <v>346.6116753810107</v>
       </c>
       <c r="N38" t="n">
-        <v>276.4003148537548</v>
+        <v>318.9109546372723</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10890,10 +10890,10 @@
         <v>45.35538097313157</v>
       </c>
       <c r="K39" t="n">
-        <v>7.523933392033513</v>
+        <v>185.5239333920335</v>
       </c>
       <c r="L39" t="n">
-        <v>154.0381173908899</v>
+        <v>144.5167869809371</v>
       </c>
       <c r="M39" t="n">
         <v>232.1447782656032</v>
@@ -10905,7 +10905,7 @@
         <v>175.9308146340064</v>
       </c>
       <c r="P39" t="n">
-        <v>168.4786695900472</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>346.6116753810107</v>
+        <v>389.1223151645282</v>
       </c>
       <c r="N41" t="n">
-        <v>318.9109546372776</v>
+        <v>276.4003148537548</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>45.35538097313157</v>
+        <v>223.3553809731316</v>
       </c>
       <c r="K42" t="n">
-        <v>185.5239333920335</v>
+        <v>7.523933392033513</v>
       </c>
       <c r="L42" t="n">
-        <v>144.5167869809371</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>232.1447782656032</v>
+        <v>410.1447782656032</v>
       </c>
       <c r="N42" t="n">
-        <v>372.1431091381671</v>
+        <v>346.1120411630635</v>
       </c>
       <c r="O42" t="n">
-        <v>175.9308146340064</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>168.4786695900472</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>346.6116753810107</v>
+        <v>389.1223151645335</v>
       </c>
       <c r="N44" t="n">
         <v>276.4003148537548</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>93.7781482316112</v>
+        <v>51.26750844808842</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,7 +11364,7 @@
         <v>45.35538097313157</v>
       </c>
       <c r="K45" t="n">
-        <v>185.5239333920335</v>
+        <v>161.5620507829234</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
         <v>232.1447782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>348.1812265290571</v>
+        <v>372.1431091381671</v>
       </c>
       <c r="O45" t="n">
         <v>175.9308146340064</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>23.04346271926163</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22591,16 +22591,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -22609,10 +22609,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>19.72518857862912</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>196.3905368347448</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22642,10 +22642,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>455.3772075117811</v>
       </c>
       <c r="T3" t="n">
-        <v>264.8765063872911</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -22660,7 +22660,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.62268818412349</v>
       </c>
     </row>
     <row r="4">
@@ -22718,7 +22718,7 @@
         <v>283.559266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>472.230868928812</v>
+        <v>303.899177161479</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22727,7 +22727,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>150.9308502908514</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -22949,13 +22949,13 @@
         <v>569.0776952265559</v>
       </c>
       <c r="P7" t="n">
-        <v>626.380356344671</v>
+        <v>423.8346211187462</v>
       </c>
       <c r="Q7" t="n">
         <v>283.559266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>701.3774700658004</v>
+        <v>303.8991771614789</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23071,13 +23071,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>143.2002089680777</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -23116,13 +23116,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>87.47770086655964</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>400.1707371186773</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>441.4834146812384</v>
+        <v>41.48341468123843</v>
       </c>
       <c r="N10" t="n">
         <v>93.49862192739742</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253.4501670096553</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>269.4745782429939</v>
@@ -23232,7 +23232,7 @@
         <v>230.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>224.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>224.8896287080119</v>
@@ -23241,7 +23241,7 @@
         <v>222.6317441463127</v>
       </c>
       <c r="H11" t="n">
-        <v>216.4818195075475</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23277,19 +23277,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>401.7481445426342</v>
       </c>
       <c r="U11" t="n">
         <v>469.1312462973544</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>449.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>254.977940875281</v>
       </c>
       <c r="X11" t="n">
-        <v>412.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23302,7 +23302,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>204.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -23317,7 +23317,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>145.137271724084</v>
       </c>
       <c r="H12" t="n">
         <v>146.3514834128362</v>
@@ -23350,13 +23350,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>320.4120917764717</v>
+        <v>329.8805897452095</v>
       </c>
       <c r="S12" t="n">
         <v>275.3772075117811</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>49.95078695350489</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -23399,7 +23399,7 @@
         <v>64.53895480874314</v>
       </c>
       <c r="H13" t="n">
-        <v>44.28194577374975</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>49.85847871917585</v>
       </c>
       <c r="L13" t="n">
-        <v>38.37985359801667</v>
+        <v>168.4800871741726</v>
       </c>
       <c r="M13" t="n">
         <v>261.4834146812384</v>
@@ -23429,7 +23429,7 @@
         <v>503.559266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>523.899177161479</v>
+        <v>438.0808893590728</v>
       </c>
       <c r="S13" t="n">
         <v>173.5741354405604</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>222.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>190.4745782429939</v>
@@ -23472,13 +23472,13 @@
         <v>145.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>145.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>143.6317441463127</v>
+        <v>1.534109722496765</v>
       </c>
       <c r="H14" t="n">
-        <v>137.4818195075475</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,13 +23511,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>210.1979165460415</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>390.1312462973544</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23526,10 +23526,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>324.604425442331</v>
+        <v>333.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>252.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>28.11380033707866</v>
       </c>
       <c r="C16" t="n">
         <v>13.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>26.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>21.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>15.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -23648,28 +23648,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>89.48008717417258</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>182.4834146812384</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>234.9188457634882</v>
       </c>
       <c r="O16" t="n">
         <v>310.0776952265559</v>
       </c>
       <c r="P16" t="n">
-        <v>367.3803563446709</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>424.559266425598</v>
+        <v>107.3247005744383</v>
       </c>
       <c r="R16" t="n">
-        <v>444.8991771614789</v>
+        <v>444.899177161479</v>
       </c>
       <c r="S16" t="n">
-        <v>37.32069291042382</v>
+        <v>94.57413544056038</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>28.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23700,10 +23700,10 @@
         <v>222.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>99.31662775344574</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>151.3391557398498</v>
+        <v>78.02705765341021</v>
       </c>
       <c r="E17" t="n">
         <v>145.3632896068686</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>210.1979165460415</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23757,13 +23757,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>370.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>333.2818334606677</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -23858,16 +23858,16 @@
         <v>28.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>13.72524664804467</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>26.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>21.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>15.38285596774193</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>89.48008717417258</v>
+        <v>89.48008717417261</v>
       </c>
       <c r="M19" t="n">
         <v>182.4834146812384</v>
@@ -23897,16 +23897,16 @@
         <v>310.0776952265559</v>
       </c>
       <c r="P19" t="n">
-        <v>367.380356344671</v>
+        <v>367.3803563446709</v>
       </c>
       <c r="Q19" t="n">
-        <v>357.0428823401053</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>184.8435213912462</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>94.57413544056035</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23943,10 +23943,10 @@
         <v>151.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>145.3632896068686</v>
+        <v>108.4306427633084</v>
       </c>
       <c r="F20" t="n">
-        <v>145.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>143.6317441463127</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>27.37564099446956</v>
+        <v>210.1979165460415</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24125,22 +24125,22 @@
         <v>89.48008717417258</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>182.4834146812384</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>234.9188457634882</v>
       </c>
       <c r="O22" t="n">
-        <v>310.0776952265559</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>367.380356344671</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>424.559266425598</v>
+        <v>417.4023958009942</v>
       </c>
       <c r="R22" t="n">
-        <v>177.6865154103748</v>
+        <v>444.899177161479</v>
       </c>
       <c r="S22" t="n">
         <v>94.57413544056038</v>
@@ -24174,10 +24174,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>190.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>83.52385015151573</v>
+        <v>151.3391557398498</v>
       </c>
       <c r="E23" t="n">
         <v>145.3632896068686</v>
@@ -24231,7 +24231,7 @@
         <v>390.1312462973544</v>
       </c>
       <c r="V23" t="n">
-        <v>370.8510241668239</v>
+        <v>112.5611403354958</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>89.48008717417261</v>
+        <v>89.48008717417258</v>
       </c>
       <c r="M25" t="n">
         <v>182.4834146812384</v>
@@ -24368,19 +24368,19 @@
         <v>234.9188457634882</v>
       </c>
       <c r="O25" t="n">
-        <v>310.0776952265559</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>367.3803563446709</v>
+        <v>367.380356344671</v>
       </c>
       <c r="Q25" t="n">
-        <v>184.8435213912462</v>
+        <v>50.02203945632311</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>444.899177161479</v>
       </c>
       <c r="S25" t="n">
-        <v>94.57413544056035</v>
+        <v>94.57413544056038</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>310.9993129555745</v>
+        <v>133.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>278.4745782429939</v>
+        <v>101.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>239.3391557398498</v>
@@ -24426,7 +24426,7 @@
         <v>231.6317441463127</v>
       </c>
       <c r="H26" t="n">
-        <v>48.48181950728849</v>
+        <v>225.4818195075475</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,25 +24459,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>121.1979165457764</v>
+        <v>298.1979165460415</v>
       </c>
       <c r="T26" t="n">
-        <v>233.7481445423695</v>
+        <v>410.7481445426342</v>
       </c>
       <c r="U26" t="n">
         <v>478.1312462973544</v>
       </c>
       <c r="V26" t="n">
-        <v>312.1202843024399</v>
+        <v>458.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>467.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>421.2818334606677</v>
+        <v>274.5510935954948</v>
       </c>
       <c r="Y26" t="n">
-        <v>340.3174326828064</v>
+        <v>163.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24493,19 +24493,19 @@
         <v>190.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>176.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>171.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>168.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>154.1372717240839</v>
+        <v>154.137271724084</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>155.3514834128362</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24535,13 +24535,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>186.7210099932806</v>
+        <v>338.8805897452095</v>
       </c>
       <c r="S27" t="n">
         <v>284.3772075117811</v>
       </c>
       <c r="T27" t="n">
-        <v>54.93021804744205</v>
+        <v>231.9302180477025</v>
       </c>
       <c r="U27" t="n">
         <v>229.1707371186773</v>
@@ -24550,7 +24550,7 @@
         <v>243.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>84.37314290959876</v>
+        <v>117.1081062020655</v>
       </c>
       <c r="X27" t="n">
         <v>248.8627394453875</v>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>116.1138003370787</v>
+        <v>2.609077303845325</v>
       </c>
       <c r="C28" t="n">
         <v>101.7252466480447</v>
@@ -24575,16 +24575,16 @@
         <v>114.5362180555555</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>109.9809048369565</v>
       </c>
       <c r="F28" t="n">
-        <v>53.18310717361667</v>
+        <v>103.3828559677419</v>
       </c>
       <c r="G28" t="n">
         <v>73.53895480874314</v>
       </c>
       <c r="H28" t="n">
-        <v>53.28194577374977</v>
+        <v>53.28194577374975</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>58.85847871917584</v>
+        <v>58.85847871917585</v>
       </c>
       <c r="L28" t="n">
         <v>177.4800871741726</v>
@@ -24608,7 +24608,7 @@
         <v>398.0776952265559</v>
       </c>
       <c r="P28" t="n">
-        <v>455.3803563446709</v>
+        <v>455.380356344671</v>
       </c>
       <c r="Q28" t="n">
         <v>512.559266425598</v>
@@ -24620,16 +24620,16 @@
         <v>182.5741354405604</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>36.86718945707739</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>28.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>55.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>76.44364543010755</v>
@@ -24648,22 +24648,22 @@
         <v>293.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>104.6921782430784</v>
+        <v>261.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>44.33915573982165</v>
+        <v>222.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>216.3632896068686</v>
+        <v>59.58088960686877</v>
       </c>
       <c r="F29" t="n">
-        <v>38.88962870798372</v>
+        <v>38.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>214.6317441463127</v>
+        <v>36.63174414631268</v>
       </c>
       <c r="H29" t="n">
-        <v>208.4818195075475</v>
+        <v>30.48181950754753</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>281.1979165460415</v>
       </c>
       <c r="T29" t="n">
-        <v>215.7481445426061</v>
+        <v>393.7481445426342</v>
       </c>
       <c r="U29" t="n">
         <v>461.1312462973544</v>
@@ -24736,13 +24736,13 @@
         <v>154.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>151.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.137271724084</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>138.3514834128362</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -24772,25 +24772,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>244.6137240547513</v>
+        <v>143.8805897452095</v>
       </c>
       <c r="S30" t="n">
         <v>267.3772075117811</v>
       </c>
       <c r="T30" t="n">
-        <v>214.9302180477025</v>
+        <v>66.53835488244729</v>
       </c>
       <c r="U30" t="n">
-        <v>34.17073711867732</v>
+        <v>212.1707371186773</v>
       </c>
       <c r="V30" t="n">
         <v>226.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>244.3731429098285</v>
+        <v>66.37314290982852</v>
       </c>
       <c r="X30" t="n">
-        <v>231.8627394453875</v>
+        <v>53.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>211.3913927661343</v>
@@ -24803,13 +24803,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>99.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>84.72524664804467</v>
+        <v>46.49268058251722</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>97.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>92.98090483695654</v>
@@ -24818,10 +24818,10 @@
         <v>86.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>56.53895480874315</v>
+        <v>56.53895480874314</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>36.28194577374975</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24830,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>41.85847871917584</v>
+        <v>41.85847871917585</v>
       </c>
       <c r="L31" t="n">
         <v>160.4800871741726</v>
@@ -24845,7 +24845,7 @@
         <v>381.0776952265559</v>
       </c>
       <c r="P31" t="n">
-        <v>438.3803563446709</v>
+        <v>438.380356344671</v>
       </c>
       <c r="Q31" t="n">
         <v>495.559266425598</v>
@@ -24857,22 +24857,22 @@
         <v>165.5741354405604</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>19.86718945707739</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>11.17031021621619</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>38.37280983870968</v>
       </c>
       <c r="X31" t="n">
         <v>59.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>65.88210693870241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -24885,22 +24885,22 @@
         <v>293.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>104.6921782430863</v>
+        <v>261.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>44.33915573981901</v>
+        <v>222.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>38.3632896068379</v>
+        <v>38.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>38.88962870798107</v>
+        <v>216.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>214.6317441463127</v>
+        <v>36.63174414631269</v>
       </c>
       <c r="H32" t="n">
-        <v>208.4818195075475</v>
+        <v>30.48181950754751</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>393.7481445426342</v>
       </c>
       <c r="U32" t="n">
-        <v>461.1312462973544</v>
+        <v>304.3488462973545</v>
       </c>
       <c r="V32" t="n">
         <v>441.8510241668239</v>
@@ -24982,7 +24982,7 @@
         <v>138.3514834128362</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>8.390536834744758</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25009,22 +25009,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>321.8805897452095</v>
+        <v>165.0981897452096</v>
       </c>
       <c r="S33" t="n">
-        <v>118.9853443465259</v>
+        <v>89.37720751178112</v>
       </c>
       <c r="T33" t="n">
-        <v>36.9302180477025</v>
+        <v>214.9302180477025</v>
       </c>
       <c r="U33" t="n">
         <v>212.1707371186773</v>
       </c>
       <c r="V33" t="n">
-        <v>48.51066719152016</v>
+        <v>226.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>244.3731429098285</v>
+        <v>66.37314290982852</v>
       </c>
       <c r="X33" t="n">
         <v>53.86273944538755</v>
@@ -25040,7 +25040,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>99.11380033707866</v>
       </c>
       <c r="C34" t="n">
         <v>84.72524664804467</v>
@@ -25082,7 +25082,7 @@
         <v>381.0776952265559</v>
       </c>
       <c r="P34" t="n">
-        <v>438.3803563446709</v>
+        <v>307.2608923783555</v>
       </c>
       <c r="Q34" t="n">
         <v>495.559266425598</v>
@@ -25109,7 +25109,7 @@
         <v>59.44364543010755</v>
       </c>
       <c r="Y34" t="n">
-        <v>67.45968922022561</v>
+        <v>99.46535284946236</v>
       </c>
     </row>
     <row r="35">
@@ -25128,16 +25128,16 @@
         <v>222.3391557398498</v>
       </c>
       <c r="E35" t="n">
-        <v>216.3632896068686</v>
+        <v>59.58088960686877</v>
       </c>
       <c r="F35" t="n">
-        <v>216.8896287080119</v>
+        <v>38.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>214.6317441463127</v>
+        <v>36.63174414631269</v>
       </c>
       <c r="H35" t="n">
-        <v>208.4818195075475</v>
+        <v>30.48181950754751</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>103.1979165459844</v>
+        <v>281.1979165460415</v>
       </c>
       <c r="T35" t="n">
         <v>393.7481445426342</v>
@@ -25179,13 +25179,13 @@
         <v>461.1312462973544</v>
       </c>
       <c r="V35" t="n">
-        <v>263.8510241667668</v>
+        <v>441.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>272.3734759808904</v>
+        <v>450.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>247.499433460839</v>
+        <v>404.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>323.3174326828064</v>
@@ -25198,10 +25198,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18.55655664632661</v>
+        <v>140.7533610635109</v>
       </c>
       <c r="C36" t="n">
-        <v>173.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>159.9376868977026</v>
@@ -25213,10 +25213,10 @@
         <v>151.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>137.1372717240839</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>138.3514834128362</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25246,7 +25246,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>321.8805897452095</v>
+        <v>143.8805897452095</v>
       </c>
       <c r="S36" t="n">
         <v>267.3772075117811</v>
@@ -25255,10 +25255,10 @@
         <v>214.9302180477025</v>
       </c>
       <c r="U36" t="n">
-        <v>34.17073711867732</v>
+        <v>212.1707371186773</v>
       </c>
       <c r="V36" t="n">
-        <v>48.51066719152016</v>
+        <v>226.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>244.3731429098285</v>
@@ -25267,7 +25267,7 @@
         <v>231.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>62.99952960087913</v>
+        <v>211.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -25286,7 +25286,7 @@
         <v>97.53621805555548</v>
       </c>
       <c r="E37" t="n">
-        <v>3.719919589816953</v>
+        <v>92.98090483695654</v>
       </c>
       <c r="F37" t="n">
         <v>86.38285596774193</v>
@@ -25295,7 +25295,7 @@
         <v>56.53895480874315</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>36.28194577374977</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -25343,10 +25343,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>59.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>99.46535284946236</v>
+        <v>33.36606725868054</v>
       </c>
     </row>
     <row r="38">
@@ -25368,13 +25368,13 @@
         <v>216.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>216.8896287080119</v>
+        <v>38.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>214.6317441463127</v>
+        <v>57.84934414631272</v>
       </c>
       <c r="H38" t="n">
-        <v>208.4818195075475</v>
+        <v>30.48181950754753</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25413,19 +25413,19 @@
         <v>393.7481445426342</v>
       </c>
       <c r="U38" t="n">
-        <v>304.3488462975564</v>
+        <v>461.1312462973544</v>
       </c>
       <c r="V38" t="n">
-        <v>263.8510241667566</v>
+        <v>441.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>272.3734759808802</v>
+        <v>450.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>226.2818334606004</v>
+        <v>404.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>323.3174326828064</v>
+        <v>145.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -25441,7 +25441,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>6.645736177966683</v>
+        <v>159.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>154.6720972219126</v>
@@ -25483,7 +25483,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>143.8805897452095</v>
+        <v>321.8805897452095</v>
       </c>
       <c r="S39" t="n">
         <v>267.3772075117811</v>
@@ -25495,13 +25495,13 @@
         <v>212.1707371186773</v>
       </c>
       <c r="V39" t="n">
-        <v>226.5106671915202</v>
+        <v>73.21871647178426</v>
       </c>
       <c r="W39" t="n">
         <v>244.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>231.8627394453875</v>
+        <v>53.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>211.3913927661343</v>
@@ -25517,22 +25517,22 @@
         <v>99.11380033707866</v>
       </c>
       <c r="C40" t="n">
-        <v>84.72524664804467</v>
+        <v>38.43065028848821</v>
       </c>
       <c r="D40" t="n">
-        <v>97.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>92.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>86.38285596774193</v>
       </c>
       <c r="G40" t="n">
-        <v>53.66082552934544</v>
+        <v>56.53895480874314</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>36.28194577374975</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>41.85847871917585</v>
       </c>
       <c r="L40" t="n">
         <v>160.4800871741726</v>
@@ -25568,16 +25568,16 @@
         <v>165.5741354405604</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>19.86718945707739</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>11.17031021621619</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>38.37280983870968</v>
       </c>
       <c r="X40" t="n">
         <v>59.44364543010755</v>
@@ -25593,13 +25593,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>324.073153878949</v>
+        <v>385.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>353.4745782429939</v>
+        <v>207.3775590312062</v>
       </c>
       <c r="D41" t="n">
-        <v>136.3391557397381</v>
+        <v>136.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>308.3632896068686</v>
@@ -25608,10 +25608,10 @@
         <v>308.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>306.6317441463127</v>
+        <v>128.6317441463127</v>
       </c>
       <c r="H41" t="n">
-        <v>300.4818195075475</v>
+        <v>122.4818195075475</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>84.17086013482708</v>
       </c>
       <c r="S41" t="n">
         <v>373.1979165460415</v>
       </c>
       <c r="T41" t="n">
-        <v>307.7481445425225</v>
+        <v>485.7481445426342</v>
       </c>
       <c r="U41" t="n">
         <v>553.1312462973544</v>
@@ -25659,7 +25659,7 @@
         <v>542.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>318.281833460556</v>
+        <v>496.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>415.3174326828064</v>
@@ -25684,7 +25684,7 @@
         <v>246.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>65.63624233787687</v>
+        <v>243.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>229.1372717240839</v>
@@ -25723,13 +25723,13 @@
         <v>413.8805897452095</v>
       </c>
       <c r="S42" t="n">
-        <v>359.3772075117811</v>
+        <v>303.1861188709678</v>
       </c>
       <c r="T42" t="n">
-        <v>306.9302180477025</v>
+        <v>128.9302180477025</v>
       </c>
       <c r="U42" t="n">
-        <v>304.1707371186773</v>
+        <v>126.1707371186773</v>
       </c>
       <c r="V42" t="n">
         <v>140.5106671915202</v>
@@ -25738,10 +25738,10 @@
         <v>336.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>145.8627394453875</v>
+        <v>323.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>247.200304125321</v>
+        <v>303.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25769,10 +25769,10 @@
         <v>148.5389548087431</v>
       </c>
       <c r="H43" t="n">
-        <v>128.2819457737498</v>
+        <v>88.70297222851042</v>
       </c>
       <c r="I43" t="n">
-        <v>25.87021977979697</v>
+        <v>65.4491933250363</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>481.9993129555745</v>
+        <v>431.9022937437868</v>
       </c>
       <c r="C44" t="n">
         <v>449.4745782429939</v>
@@ -25842,13 +25842,13 @@
         <v>404.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>404.8896287080119</v>
+        <v>226.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>402.6317441463127</v>
+        <v>224.6317441463127</v>
       </c>
       <c r="H44" t="n">
-        <v>218.4818195073893</v>
+        <v>396.4818195075475</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.170860134668942</v>
+        <v>2.17086013482708</v>
       </c>
       <c r="S44" t="n">
         <v>469.1979165460415</v>
@@ -25890,13 +25890,13 @@
         <v>649.1312462973544</v>
       </c>
       <c r="V44" t="n">
-        <v>579.7540049555106</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>638.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>414.2818334605096</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>511.3174326828064</v>
@@ -25912,7 +25912,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>183.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>169.9376868977026</v>
@@ -25927,10 +25927,10 @@
         <v>264.5556462485259</v>
       </c>
       <c r="H45" t="n">
-        <v>326.3514834128362</v>
+        <v>148.3514834128362</v>
       </c>
       <c r="I45" t="n">
-        <v>18.39053683474476</v>
+        <v>196.3905368347448</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25960,7 +25960,7 @@
         <v>509.8805897452095</v>
       </c>
       <c r="S45" t="n">
-        <v>277.3772075117811</v>
+        <v>455.3772075117811</v>
       </c>
       <c r="T45" t="n">
         <v>402.9302180477025</v>
@@ -26042,10 +26042,10 @@
         <v>353.5741354405604</v>
       </c>
       <c r="T46" t="n">
-        <v>207.8671894570774</v>
+        <v>207.4469656209867</v>
       </c>
       <c r="U46" t="n">
-        <v>150.5106264547607</v>
+        <v>150.9308502908514</v>
       </c>
       <c r="V46" t="n">
         <v>199.1703102162162</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3173086.79817931</v>
+        <v>3173086.798179311</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3958547.818573289</v>
+        <v>3958547.81857329</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4900554.26889691</v>
+        <v>4900554.268896912</v>
       </c>
     </row>
     <row r="7">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6784567.16954415</v>
+        <v>6784567.169544145</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8278897.070774458</v>
+        <v>8278897.070774459</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8946865.860192429</v>
+        <v>8946865.860192431</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10282370.7203213</v>
+        <v>10282370.72032131</v>
       </c>
     </row>
     <row r="14">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11426481.89971921</v>
+        <v>11426481.89971922</v>
       </c>
     </row>
     <row r="16">
@@ -26275,43 +26275,43 @@
         <v>1066138.120051577</v>
       </c>
       <c r="D2" t="n">
-        <v>1066138.120051578</v>
+        <v>1066138.120051579</v>
       </c>
       <c r="E2" t="n">
-        <v>831664.6098289172</v>
+        <v>831664.6098289173</v>
       </c>
       <c r="F2" t="n">
-        <v>997418.5944603046</v>
+        <v>997418.594460304</v>
       </c>
       <c r="G2" t="n">
-        <v>997418.5944603041</v>
+        <v>997418.5944603047</v>
       </c>
       <c r="H2" t="n">
         <v>997418.5944603041</v>
       </c>
       <c r="I2" t="n">
-        <v>997418.5944603048</v>
+        <v>997418.5944603042</v>
       </c>
       <c r="J2" t="n">
-        <v>669948.9327889172</v>
+        <v>669948.9327889164</v>
       </c>
       <c r="K2" t="n">
-        <v>707031.984774117</v>
+        <v>707031.9847741168</v>
       </c>
       <c r="L2" t="n">
-        <v>707031.9847741165</v>
+        <v>707031.9847741167</v>
       </c>
       <c r="M2" t="n">
-        <v>707031.984774117</v>
+        <v>707031.9847741168</v>
       </c>
       <c r="N2" t="n">
-        <v>707031.9847741168</v>
+        <v>707031.9847741169</v>
       </c>
       <c r="O2" t="n">
         <v>504379.8522354491</v>
       </c>
       <c r="P2" t="n">
-        <v>282338.5568754493</v>
+        <v>282338.5568754494</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>560885.7755050703</v>
+        <v>563758.4666253094</v>
       </c>
       <c r="C4" t="n">
-        <v>559245.803677797</v>
+        <v>562118.4947980361</v>
       </c>
       <c r="D4" t="n">
-        <v>557603.6071263808</v>
+        <v>560476.2982466205</v>
       </c>
       <c r="E4" t="n">
-        <v>408563.4709025798</v>
+        <v>411436.1620228189</v>
       </c>
       <c r="F4" t="n">
-        <v>511482.5416090162</v>
+        <v>514355.2327292553</v>
       </c>
       <c r="G4" t="n">
-        <v>510009.2197568993</v>
+        <v>512881.9108771386</v>
       </c>
       <c r="H4" t="n">
-        <v>508533.8530181255</v>
+        <v>511406.544138365</v>
       </c>
       <c r="I4" t="n">
-        <v>507056.4266434382</v>
+        <v>509929.1177636773</v>
       </c>
       <c r="J4" t="n">
-        <v>310848.1835717435</v>
+        <v>312204.8687913261</v>
       </c>
       <c r="K4" t="n">
-        <v>332562.9247534642</v>
+        <v>333923.689291282</v>
       </c>
       <c r="L4" t="n">
-        <v>331464.7236806531</v>
+        <v>332825.488218471</v>
       </c>
       <c r="M4" t="n">
-        <v>330364.9529809074</v>
+        <v>331725.7175187253</v>
       </c>
       <c r="N4" t="n">
-        <v>329263.6009937712</v>
+        <v>330624.365531589</v>
       </c>
       <c r="O4" t="n">
-        <v>205893.6394539771</v>
+        <v>207254.4039917949</v>
       </c>
       <c r="P4" t="n">
-        <v>71947.09771164741</v>
+        <v>73307.86224946547</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-18007.25545349406</v>
+        <v>-20879.94657373338</v>
       </c>
       <c r="C6" t="n">
-        <v>436152.7163737796</v>
+        <v>433280.0252535407</v>
       </c>
       <c r="D6" t="n">
-        <v>437794.9129251969</v>
+        <v>434922.2218049582</v>
       </c>
       <c r="E6" t="n">
-        <v>226856.7189263374</v>
+        <v>223984.0278060984</v>
       </c>
       <c r="F6" t="n">
-        <v>363850.1818512884</v>
+        <v>360977.4907310487</v>
       </c>
       <c r="G6" t="n">
-        <v>428523.5037034049</v>
+        <v>425650.8125831661</v>
       </c>
       <c r="H6" t="n">
-        <v>429998.8704421786</v>
+        <v>427126.1793219392</v>
       </c>
       <c r="I6" t="n">
-        <v>431476.2968168667</v>
+        <v>428603.605696627</v>
       </c>
       <c r="J6" t="n">
-        <v>191955.3502171737</v>
+        <v>190598.6649975903</v>
       </c>
       <c r="K6" t="n">
-        <v>264585.6880206529</v>
+        <v>263224.9234828348</v>
       </c>
       <c r="L6" t="n">
-        <v>342835.8890934634</v>
+        <v>341475.1245556456</v>
       </c>
       <c r="M6" t="n">
-        <v>343935.6597932096</v>
+        <v>342574.8952553915</v>
       </c>
       <c r="N6" t="n">
-        <v>345037.0117803456</v>
+        <v>343676.2472425279</v>
       </c>
       <c r="O6" t="n">
-        <v>273489.188781472</v>
+        <v>272128.4242436543</v>
       </c>
       <c r="P6" t="n">
-        <v>193465.0591638019</v>
+        <v>192104.2946259839</v>
       </c>
     </row>
   </sheetData>
@@ -26987,13 +26987,13 @@
         <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>-0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>92</v>
@@ -27005,7 +27005,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27445,13 +27445,13 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>242.8726025844348</v>
       </c>
       <c r="I2" t="n">
         <v>106.6853807882123</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>180.1708601348271</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,25 +27512,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>306.6262948342071</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27560,16 +27560,16 @@
         <v>96.20077452444184</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>400</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>400</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27597,7 +27597,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>285.1159942194648</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27639,16 +27639,16 @@
         <v>400</v>
       </c>
       <c r="R4" t="n">
-        <v>231.668308232667</v>
+        <v>400</v>
       </c>
       <c r="S4" t="n">
         <v>353.5741354405604</v>
       </c>
       <c r="T4" t="n">
-        <v>207.4469656209867</v>
+        <v>207.8671894570774</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9308502908514</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>396.4818195075475</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>129.7288435074734</v>
+        <v>180.1708601348271</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>400</v>
+        <v>353.0761638650994</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27749,10 +27749,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>68.58128712164404</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -27764,13 +27764,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.137271724084</v>
       </c>
       <c r="H6" t="n">
-        <v>326.3514834128362</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>196.3905368347448</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>96.20077452444184</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27809,7 +27809,7 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>253.8056629836297</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27870,13 +27870,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>202.5457352259249</v>
       </c>
       <c r="Q7" t="n">
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>2.521707095678645</v>
+        <v>400</v>
       </c>
       <c r="S7" t="n">
         <v>353.5741354405604</v>
@@ -27885,7 +27885,7 @@
         <v>207.8671894570774</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9308502908514</v>
+        <v>150.5106264547607</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.0451290133716</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>242.8726025844344</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>348.2405506898403</v>
       </c>
       <c r="I8" t="n">
-        <v>106.6853807882123</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>1.317432682806384</v>
       </c>
     </row>
     <row r="9">
@@ -27986,22 +27986,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>369.549263917586</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>221.2495334729621</v>
       </c>
       <c r="H9" t="n">
         <v>326.3514834128362</v>
@@ -28031,28 +28031,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>96.20077452444184</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
+        <v>367.8995066452215</v>
+      </c>
+      <c r="T9" t="n">
         <v>400</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -28098,7 +28098,7 @@
         <v>348.4800871741726</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N10" t="n">
         <v>400</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>96.20077452440944</v>
+        <v>96.20077452442519</v>
       </c>
       <c r="R12" t="n">
         <v>180</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>96.20077452440043</v>
+        <v>93.88071994692652</v>
       </c>
       <c r="R15" t="n">
         <v>259</v>
@@ -28517,7 +28517,7 @@
         <v>259</v>
       </c>
       <c r="U15" t="n">
-        <v>256.6799454224996</v>
+        <v>259</v>
       </c>
       <c r="V15" t="n">
         <v>259</v>
@@ -28718,7 +28718,7 @@
         <v>259</v>
       </c>
       <c r="I18" t="n">
-        <v>194.0704822571651</v>
+        <v>196.3905368347448</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>96.20077452444184</v>
+        <v>93.88071994692652</v>
       </c>
       <c r="R18" t="n">
         <v>259</v>
@@ -28943,13 +28943,13 @@
         <v>259</v>
       </c>
       <c r="E21" t="n">
-        <v>259</v>
+        <v>256.6799454224995</v>
       </c>
       <c r="F21" t="n">
         <v>259</v>
       </c>
       <c r="G21" t="n">
-        <v>256.6799454223807</v>
+        <v>259</v>
       </c>
       <c r="H21" t="n">
         <v>259</v>
@@ -29216,10 +29216,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>96.20077452444184</v>
+        <v>93.88071994692473</v>
       </c>
       <c r="R24" t="n">
-        <v>256.6799454224994</v>
+        <v>259</v>
       </c>
       <c r="S24" t="n">
         <v>259</v>
@@ -33239,7 +33239,7 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L29" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M29" t="n">
         <v>197.6504522613065</v>
@@ -33476,7 +33476,7 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L32" t="n">
-        <v>177.6325628140725</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M32" t="n">
         <v>197.6504522613065</v>
@@ -33713,7 +33713,7 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L35" t="n">
-        <v>177.6325628140732</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M35" t="n">
         <v>197.6504522613065</v>
@@ -33950,7 +33950,7 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L38" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M38" t="n">
         <v>197.6504522613065</v>
@@ -34187,7 +34187,7 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L41" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M41" t="n">
         <v>197.6504522613065</v>
@@ -34746,13 +34746,13 @@
         <v>60.49327516194486</v>
       </c>
       <c r="K2" t="n">
-        <v>480.2806189723967</v>
+        <v>143.1841206030151</v>
       </c>
       <c r="L2" t="n">
         <v>177.6325628140704</v>
       </c>
       <c r="M2" t="n">
-        <v>510</v>
+        <v>337.0964983693813</v>
       </c>
       <c r="N2" t="n">
         <v>510</v>
@@ -34764,7 +34764,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34989,16 +34989,16 @@
         <v>177.6325628140704</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>416.7917617832245</v>
       </c>
       <c r="N5" t="n">
-        <v>68.37143541088474</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>119.4078088178674</v>
       </c>
       <c r="P5" t="n">
-        <v>510</v>
+        <v>161.5796736276603</v>
       </c>
       <c r="Q5" t="n">
         <v>510</v>
@@ -35062,13 +35062,13 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K6" t="n">
-        <v>288.1867919472067</v>
+        <v>288.35630747098</v>
       </c>
       <c r="L6" t="n">
         <v>404.8592998769889</v>
       </c>
       <c r="M6" t="n">
-        <v>239.5500421645042</v>
+        <v>239.380526640731</v>
       </c>
       <c r="N6" t="n">
         <v>291.2654180331832</v>
@@ -35220,7 +35220,7 @@
         <v>60.49327516194486</v>
       </c>
       <c r="K8" t="n">
-        <v>480.2806189723967</v>
+        <v>143.1841206030151</v>
       </c>
       <c r="L8" t="n">
         <v>177.6325628140704</v>
@@ -35238,7 +35238,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>337.0964983693814</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35299,7 +35299,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K9" t="n">
-        <v>288.1867919472205</v>
+        <v>288.186791947231</v>
       </c>
       <c r="L9" t="n">
         <v>404.8592998769889</v>
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>490.7980117481015</v>
+        <v>60.49327516194486</v>
       </c>
       <c r="K11" t="n">
         <v>143.1841206030151</v>
@@ -35466,7 +35466,7 @@
         <v>510</v>
       </c>
       <c r="N11" t="n">
-        <v>416.7917617832247</v>
+        <v>337.0964983693812</v>
       </c>
       <c r="O11" t="n">
         <v>119.4078088178674</v>
@@ -35475,7 +35475,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35536,7 +35536,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K12" t="n">
-        <v>288.1867919472398</v>
+        <v>288.1867919472237</v>
       </c>
       <c r="L12" t="n">
         <v>404.8592998769889</v>
@@ -35694,7 +35694,7 @@
         <v>60.49327516194486</v>
       </c>
       <c r="K14" t="n">
-        <v>480.2806189723967</v>
+        <v>143.1841206030151</v>
       </c>
       <c r="L14" t="n">
         <v>177.6325628140704</v>
@@ -35712,7 +35712,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>337.0964983693814</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K15" t="n">
-        <v>288.35630747098</v>
+        <v>288.1867919472218</v>
       </c>
       <c r="L15" t="n">
         <v>404.8592998769889</v>
@@ -35785,7 +35785,7 @@
         <v>291.2654180331832</v>
       </c>
       <c r="O15" t="n">
-        <v>384.5814686431661</v>
+        <v>384.7509841668973</v>
       </c>
       <c r="P15" t="n">
         <v>228.6720422505023</v>
@@ -35840,10 +35840,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>14.46104519125685</v>
+        <v>14.46104519125686</v>
       </c>
       <c r="H16" t="n">
-        <v>34.71805422625023</v>
+        <v>34.71805422625025</v>
       </c>
       <c r="I16" t="n">
         <v>97.5508066749637</v>
@@ -35852,7 +35852,7 @@
         <v>259.428756082125</v>
       </c>
       <c r="K16" t="n">
-        <v>29.14152128082416</v>
+        <v>29.14152128082415</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>60.49327516194486</v>
+        <v>490.7980117481015</v>
       </c>
       <c r="K17" t="n">
         <v>143.1841206030151</v>
       </c>
       <c r="L17" t="n">
-        <v>177.6325628140704</v>
+        <v>510</v>
       </c>
       <c r="M17" t="n">
-        <v>337.0964983693813</v>
+        <v>510</v>
       </c>
       <c r="N17" t="n">
-        <v>510</v>
+        <v>84.42432459729513</v>
       </c>
       <c r="O17" t="n">
         <v>119.4078088178674</v>
@@ -35949,7 +35949,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q17" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36010,7 +36010,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K18" t="n">
-        <v>288.1867919472875</v>
+        <v>288.1867919472218</v>
       </c>
       <c r="L18" t="n">
         <v>404.8592998769889</v>
@@ -36077,10 +36077,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>14.46104519125686</v>
+        <v>14.46104519125685</v>
       </c>
       <c r="H19" t="n">
-        <v>34.71805422625025</v>
+        <v>34.71805422625023</v>
       </c>
       <c r="I19" t="n">
         <v>97.5508066749637</v>
@@ -36089,7 +36089,7 @@
         <v>259.428756082125</v>
       </c>
       <c r="K19" t="n">
-        <v>29.14152128082415</v>
+        <v>29.14152128082416</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36174,19 +36174,19 @@
         <v>177.6325628140704</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>510</v>
       </c>
-      <c r="N20" t="n">
-        <v>416.7917617832247</v>
-      </c>
       <c r="O20" t="n">
-        <v>119.4078088178674</v>
+        <v>510</v>
       </c>
       <c r="P20" t="n">
         <v>161.5796736276603</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>26.19957060109199</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K21" t="n">
-        <v>288.1867919473279</v>
+        <v>288.1867919472067</v>
       </c>
       <c r="L21" t="n">
         <v>404.8592998769889</v>
@@ -36405,22 +36405,22 @@
         <v>490.7980117481015</v>
       </c>
       <c r="K23" t="n">
-        <v>510</v>
+        <v>143.1841206030151</v>
       </c>
       <c r="L23" t="n">
-        <v>177.6325628140703</v>
+        <v>177.6325628140704</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>68.37143541088474</v>
       </c>
       <c r="N23" t="n">
-        <v>49.97588238623973</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>119.4078088178674</v>
       </c>
       <c r="P23" t="n">
-        <v>161.5796736276603</v>
+        <v>510</v>
       </c>
       <c r="Q23" t="n">
         <v>510</v>
@@ -36484,7 +36484,7 @@
         <v>182.1093609546568</v>
       </c>
       <c r="K24" t="n">
-        <v>288.35630747098</v>
+        <v>288.1867919472237</v>
       </c>
       <c r="L24" t="n">
         <v>404.8592998769889</v>
@@ -36496,7 +36496,7 @@
         <v>291.2654180331832</v>
       </c>
       <c r="O24" t="n">
-        <v>384.5814686431239</v>
+        <v>384.7509841668973</v>
       </c>
       <c r="P24" t="n">
         <v>228.6720422505023</v>
@@ -36551,10 +36551,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>14.46104519125685</v>
+        <v>14.46104519125686</v>
       </c>
       <c r="H25" t="n">
-        <v>34.71805422625023</v>
+        <v>34.71805422625025</v>
       </c>
       <c r="I25" t="n">
         <v>97.5508066749637</v>
@@ -36563,7 +36563,7 @@
         <v>259.428756082125</v>
       </c>
       <c r="K25" t="n">
-        <v>29.14152128082416</v>
+        <v>29.14152128082415</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36651,7 +36651,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>39.18360663799721</v>
       </c>
       <c r="O26" t="n">
         <v>119.4078088178674</v>
@@ -36660,7 +36660,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q26" t="n">
-        <v>39.18360663799721</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36727,16 +36727,16 @@
         <v>16.76996341719079</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="N27" t="n">
-        <v>151.0093360653004</v>
+        <v>141.4880056553475</v>
       </c>
       <c r="O27" t="n">
         <v>2.069185365993604</v>
       </c>
       <c r="P27" t="n">
-        <v>177</v>
+        <v>9.52133040995281</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36794,7 +36794,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>9.550806674963697</v>
+        <v>9.550806674963692</v>
       </c>
       <c r="J28" t="n">
         <v>171.428756082125</v>
@@ -36830,7 +36830,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>20.06914970914862</v>
+        <v>20.06914970914863</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -36882,10 +36882,10 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L29" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M29" t="n">
-        <v>42.51063978352277</v>
+        <v>42.51063978351743</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -36955,7 +36955,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>159.2175650321342</v>
+        <v>178</v>
       </c>
       <c r="K30" t="n">
         <v>178</v>
@@ -36964,7 +36964,7 @@
         <v>178</v>
       </c>
       <c r="M30" t="n">
-        <v>178</v>
+        <v>159.2175650321343</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -37031,7 +37031,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>26.5508066749637</v>
+        <v>26.55080667496369</v>
       </c>
       <c r="J31" t="n">
         <v>178</v>
@@ -37067,7 +37067,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>37.06914970914862</v>
+        <v>37.06914970914863</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -37119,10 +37119,10 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L32" t="n">
-        <v>177.6325628140725</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M32" t="n">
-        <v>42.5106397835207</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -37134,7 +37134,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>42.51063978351748</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="K33" t="n">
         <v>178</v>
       </c>
       <c r="L33" t="n">
-        <v>170.8080808080807</v>
+        <v>159.2175650321342</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="O33" t="n">
-        <v>178</v>
+        <v>2.069185365993604</v>
       </c>
       <c r="P33" t="n">
-        <v>178</v>
+        <v>9.52133040995281</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37356,13 +37356,13 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L35" t="n">
-        <v>177.6325628140731</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>42.51063978352001</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>119.4078088178674</v>
@@ -37371,7 +37371,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>42.51063978351748</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,22 +37429,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>159.2175650321342</v>
+      </c>
+      <c r="L36" t="n">
         <v>178</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>178</v>
       </c>
-      <c r="L36" t="n">
-        <v>16.76996341719079</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
-        <v>144.5167869809371</v>
+        <v>178</v>
       </c>
       <c r="O36" t="n">
-        <v>178</v>
+        <v>2.069185365993604</v>
       </c>
       <c r="P36" t="n">
         <v>9.52133040995281</v>
@@ -37593,13 +37593,13 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L38" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M38" t="n">
-        <v>42.51063978352277</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>42.51063978351743</v>
       </c>
       <c r="O38" t="n">
         <v>119.4078088178674</v>
@@ -37669,10 +37669,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="L39" t="n">
-        <v>170.8080808080807</v>
+        <v>161.2867503981279</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -37684,7 +37684,7 @@
         <v>178</v>
       </c>
       <c r="P39" t="n">
-        <v>178</v>
+        <v>9.52133040995281</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37830,13 +37830,13 @@
         <v>143.1841206030151</v>
       </c>
       <c r="L41" t="n">
-        <v>177.6325628140704</v>
+        <v>177.6325628140758</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>42.51063978351743</v>
       </c>
       <c r="N41" t="n">
-        <v>42.51063978352277</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>119.4078088178674</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>16.76996341719079</v>
+      </c>
+      <c r="M42" t="n">
         <v>178</v>
       </c>
-      <c r="L42" t="n">
-        <v>161.2867503981279</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
+        <v>151.9689320248963</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.069185365993604</v>
+      </c>
+      <c r="P42" t="n">
         <v>178</v>
-      </c>
-      <c r="O42" t="n">
-        <v>178</v>
-      </c>
-      <c r="P42" t="n">
-        <v>9.52133040995281</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38070,7 +38070,7 @@
         <v>177.6325628140704</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>42.51063978352277</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -38082,7 +38082,7 @@
         <v>161.5796736276603</v>
       </c>
       <c r="Q44" t="n">
-        <v>42.51063978352277</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>178</v>
+        <v>154.03811739089</v>
       </c>
       <c r="L45" t="n">
         <v>16.76996341719079</v>
@@ -38152,7 +38152,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>154.03811739089</v>
+        <v>178</v>
       </c>
       <c r="O45" t="n">
         <v>178</v>
